--- a/quizzes/peinture-18e-niveau3.xlsx
+++ b/quizzes/peinture-18e-niveau3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978CD74C-9B0A-4C8B-BC7D-CCA03C279263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CFBC93-0347-464B-8EAE-9354DF528D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="640">
   <si>
     <t>image</t>
   </si>
@@ -92,9 +92,6 @@
     <t>L'Enseigne de Gersaint</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9c/Jean-Antoine_Watteau_-_Mezzetin.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1718-1720</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>Le Déjeuner</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1742</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>Madame de Pompadour</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/f0/Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1751</t>
   </si>
   <si>
@@ -215,9 +206,6 @@
     <t>La Prière avant le repas</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Jean_sim%C3%A9on_chardin%2C_bicchier_d%27acqua_e_caffettiera%2C_1761_ca.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1760</t>
   </si>
   <si>
@@ -236,9 +224,6 @@
     <t>Les Bulles de savon</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Jacques-Louis_David%2C_Le_Serment_des_Horaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jacques-Louis David</t>
   </si>
   <si>
@@ -248,9 +233,6 @@
     <t>Le Serment des Horaces</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/aa/Death_of_Marat_by_David.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1793</t>
   </si>
   <si>
@@ -260,27 +242,15 @@
     <t>La Mort de Marat</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Châyeau de Versailles</t>
   </si>
   <si>
     <t>Le Serment du Jeu de Paume</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>L'Enlèvement des Sabines</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Élisabeth Vigée Le Brun</t>
-  </si>
-  <si>
     <t>1787</t>
   </si>
   <si>
@@ -353,9 +323,6 @@
     <t>Jean-Marc Nattier</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Madame_Marsollier_and_Her_Daughter_MET_DP247889.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Marie Leszczińska</t>
   </si>
   <si>
@@ -434,9 +401,6 @@
     <t>Vue du port de Bordeaux</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/eb/Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1772</t>
   </si>
   <si>
@@ -548,9 +512,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/archive/7/77/20210804182123%21Joshua_Reynolds_-_Portrait_of_Nelly_O%27Brien_WLC_WLC_P38-001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UK.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/05/Jean-Baptiste_Greuze_001FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -632,9 +593,6 @@
     <t>A Lion Attacking a Horse</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Johann Zoffany</t>
   </si>
   <si>
@@ -782,9 +740,6 @@
     <t>Watson and the Shark</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d8/John_Singleton_Copley_-_Watson_and_the_Shark_%281778%29_-_NGA_Washington.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Rome from the Villa Madama</t>
   </si>
   <si>
@@ -881,9 +836,6 @@
     <t>Apothéose de la famille Pisani</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/03/The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1767-1769</t>
   </si>
   <si>
@@ -893,9 +845,6 @@
     <t>L'Immaculée Conception</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Canaletto</t>
   </si>
   <si>
@@ -905,24 +854,9 @@
     <t>Le Bassin de San Marco</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>La Piazza San Marco</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Canaletto_%28Giovanni_Antonio_Canal%29_-_The_Grand_Canal%2C_Venice%2C_Looking_South_toward_the_Rialto_Bridge_-_2019.141.2_-_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1725</t>
-  </si>
-  <si>
-    <t>Le Grand Canal depuis le pont du Rialto</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>La Régate sur le Grand Canal</t>
   </si>
   <si>
@@ -953,9 +887,6 @@
     <t>Galeries nationales d’Écosse, Edimbourg</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pietro Longhi</t>
   </si>
   <si>
@@ -1016,9 +947,6 @@
     <t>Portrait de jeune fille au singe</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Gustavus_Hamilton_%281710%E2%80%931746%29%2C_Second_Viscount_Boyne%2C_in_Masquerade_Costume_MET_DP161652.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1730-1731</t>
   </si>
   <si>
@@ -1037,9 +965,6 @@
     <t>Portrait de Thomas William Coke</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Pompeo_Batoni_-_Emperor_Joseph_II_with_Grand_Duke_Pietro_Leopoldo_of_Tuscany_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1769</t>
   </si>
   <si>
@@ -1094,27 +1019,18 @@
     <t>Vue de la ville de Vienne</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Francisco de Goya</t>
   </si>
   <si>
     <t>El Quitasol (Le Parasol)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/da/Goya.pelele.prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1791-1792</t>
   </si>
   <si>
     <t>Le Mannequin de paille</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/74/GOYA_-_El_aquelarre_%28Museo_L%C3%A1zaro_Galdiano%2C_Madrid%2C_1797-98%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1797-1798</t>
   </si>
   <si>
@@ -1124,15 +1040,9 @@
     <t>Le Sabbat des sorcières</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée des Beaux-Arts, Agen</t>
   </si>
   <si>
-    <t>Le Sommeil de la raison engendre des monstres</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Nature_morte_aux_figues%2C_par_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1145,9 +1055,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Self-portrait_Holding_an_Academic_Study_by_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9d/Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Nature morte au melon et aux poires</t>
   </si>
   <si>
@@ -1187,9 +1094,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Anton_Raphael_Mengs_-_Self-Portrait_-_WGA15040.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henry Fuseli</t>
   </si>
   <si>
@@ -1202,24 +1106,15 @@
     <t>Le Cauchemar</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Category:Titania_and_Bottom_by_F%C3%BCssli?uselang=fr#/media/File:Henry_Fuseli_-_Titania_and_Bottom.jpg</t>
-  </si>
-  <si>
     <t>1790</t>
   </si>
   <si>
     <t>Titania et Bottom</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Lady Macbeth somnambule</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/de/Johann_Heinrich_Fussli-Tor_and_Jormundgandr.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Thor combattant le serpent de Midgard</t>
   </si>
   <si>
@@ -1274,9 +1169,6 @@
     <t>Autoportrait au bonnet</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Dmitri Levitzky</t>
   </si>
   <si>
@@ -1289,9 +1181,6 @@
     <t>Portrait de Catherine II</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Dmitry_Levitzky%2C_Denis_Diderot%2C_1773%2C_Mus%C3%A9e_d%27Art_et_Histoire_de_Gen%C3%A8ve_1829-0009.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1773-1774</t>
   </si>
   <si>
@@ -1364,9 +1253,6 @@
     <t>Portrait des sœurs Gagarine</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Alexander Roslin</t>
   </si>
   <si>
@@ -1376,9 +1262,6 @@
     <t>La Dame au voile</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File:Alexander_Roslin_-_Self-portrait1.jpg#/media/File:Sj%C3%A4lvportr%C3%A4tt_(Alexander_Roslin)_-_Nationalmuseum_-_44990.tif</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Alexander_Roslin_-_Gustav_III.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1421,9 +1304,6 @@
     <t>Musée d’Art de Baltimore</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Gilbert_Stuart_-_George_Washington_%28Lansdowne_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Gilbert Stuart</t>
   </si>
   <si>
@@ -1436,15 +1316,9 @@
     <t>Portrait de George Washington (Lansdowne)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Portrait de George Washington (Athenaeum)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Charles Willson Peale</t>
   </si>
   <si>
@@ -1463,9 +1337,6 @@
     <t>Portrait de Benjamin Franklin</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Giuseppe Castiglione (Lang Shining)</t>
   </si>
   <si>
@@ -1577,9 +1448,6 @@
     <t>Autoportrait avec sa femme et sa fille</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/Nicolas_de_Largilli%C3%A8re%2C_Fran%C3%A7ois-Marie_Arouet_dit_Voltaire_adjusted.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1718</t>
   </si>
   <si>
@@ -1589,9 +1457,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Carle Van Loo</t>
-  </si>
-  <si>
     <t>1737</t>
   </si>
   <si>
@@ -1619,21 +1484,9 @@
     <t>Le chevreuil mort</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/2b/La_chasse_au_loup.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1734</t>
-  </si>
-  <si>
-    <t>Château de Fontainebleau</t>
-  </si>
-  <si>
     <t>La Chasse au loup</t>
   </si>
   <si>
-    <t>https://collections.louvre.fr/en/ark:/53355/cl010065406</t>
-  </si>
-  <si>
     <t>Nature morte au gibier</t>
   </si>
   <si>
@@ -1676,15 +1529,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Adélaïde Labille-Guiard</t>
-  </si>
-  <si>
     <t>Autoportrait avec deux élèves</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/2a/Portrait_of_Madame_Adelaide.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Portrait de Madame Adélaïde</t>
   </si>
   <si>
@@ -1721,27 +1568,18 @@
     <t>Portrait de Jean-Jacques Rousseau</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/29/An_Experiment_on_a_bird_in_an_air_pump_1768_Joseph_Wright_of_Derby_-_54977535687.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Joseph Wright of Derby</t>
   </si>
   <si>
     <t>Une expérience sur un oiseau dans une pompe à air</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b6/A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Derby Museum and Art Gallery</t>
   </si>
   <si>
     <t>Le Forgeron</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/00/Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1774-1776</t>
   </si>
   <si>
@@ -1775,9 +1613,6 @@
     <t>Portrait de Marie-Antoinette</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Ducreux_-_Autoportrait_au_bailleur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>The J. Paul Getty Museum, Los Angeles</t>
   </si>
   <si>
@@ -1802,9 +1637,6 @@
     <t>Tigre assis</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/58/%27Crows%27_by_Maruyama_Okyo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Kimbell Art Museum, Fort Worth</t>
   </si>
   <si>
@@ -1820,27 +1652,15 @@
     <t>Pins sous la neige</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Le Vieux Pin et le Paon</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9b/It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1761-1765</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/40/Ito_Jakuchu_-_Hanging_Scroll_%28white_rooster%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Le Coq blanc</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Coquillages</t>
   </si>
   <si>
@@ -1958,20 +1778,194 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Chardin_pastel_selfportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/David_Self_Portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Jean-Baptiste_Greuze_-_Self-Portrait.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg/960px-The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Canaletto_-_Rialto_Bridge_from_the_North_RCIN_400668.jpg/1280px-Canaletto_-_Rialto_Bridge_from_the_North_RCIN_400668.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Collection royale, Château de Windsor</t>
+  </si>
+  <si>
+    <t>Le Pont du Rialto vu du nord</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/da/Goya.pelele.prado.jpg/960px-Goya.pelele.prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Francisco_de_Goya_y_Lucientes_-_Witches%27_Sabbath_-_WGA10007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg/1280px-Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg/960px-A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg/1280px-Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/David_Self_Portrait.jpg/960px-David_Self_Portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Jacques-Louis_David_002.jpg/960px-Jacques-Louis_David_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg/1280px-Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/de/Johann_Heinrich_Fussli-Tor_and_Jormundgandr.jpg/960px-Johann_Heinrich_Fussli-Tor_and_Jormundgandr.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Gustavus_Hamilton%2C_2nd_Viscount_Boyne.jpg/960px-Gustavus_Hamilton%2C_2nd_Viscount_Boyne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg/1280px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg/960px-La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg/960px-Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/68/Jean-Baptiste_Oudry_-_Still_Life_with_Hare%2C_Duck%2C_Loaf_of_Bread%2C_Cheese_and_Flasks_of_Wine.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Musée d’Arts de Nantes</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Jean_Sim%C3%A9on_Chardin_-_Water_Glass_and_Jug_-_WGA04775.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Jean-Antoine_Watteau_-_Mezzetin.JPG/960px-Jean-Antoine_Watteau_-_Mezzetin.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Watsonandtheshark-original.jpg/1280px-Watsonandtheshark-original.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2a/Portrait_of_Madame_Adelaide.jpg/960px-Portrait_of_Madame_Adelaide.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ab/Madame_Marsollier_and_Her_Daughter_MET_DP247889.jpg/960px-Madame_Marsollier_and_Her_Daughter_MET_DP247889.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Dmitry_Levitzky%2C_Denis_Diderot%2C_1773%2C_Mus%C3%A9e_d%27Art_et_Histoire_de_Gen%C3%A8ve_1829-0009.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg/960px-Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg/330px-It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg/960px-%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/%27Crows%27_by_Maruyama_Okyo.jpg/500px-%27Crows%27_by_Maruyama_Okyo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg/960px-The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg/960px-Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Adélaïde LABILLE-GUIARD</t>
+  </si>
+  <si>
+    <t>Carle van LOO</t>
+  </si>
+  <si>
+    <t>Élisabeth VIGEE LE BRUN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2003,8 +1997,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2015,6 +2015,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC54F38"/>
         <bgColor rgb="FFC54F38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2068,7 +2080,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2084,7 +2096,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2423,8 +2443,8 @@
   <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="222.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.42578125" bestFit="1" customWidth="1"/>
@@ -2449,1274 +2469,1274 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>495</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>637</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>167</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
+      <c r="A3" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>498</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>637</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>499</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>633</v>
+      <c r="A5" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>20</v>
+      <c r="A6" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>404</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>8</v>
+        <v>405</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>634</v>
+        <v>502</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1750</v>
+        <v>503</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>635</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>505</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>503</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>507</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>503</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>31</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>32</v>
+      <c r="A11" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>36</v>
+      <c r="A12" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>41</v>
+      <c r="A13" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>42</v>
+        <v>216</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8</v>
+        <v>215</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>43</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>44</v>
+      <c r="A14" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>636</v>
+        <v>359</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1769</v>
+        <v>360</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>361</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8</v>
+        <v>362</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>637</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>47</v>
+        <v>364</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>360</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>49</v>
+        <v>365</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>52</v>
+        <v>342</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>8</v>
+        <v>343</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>54</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>638</v>
+        <v>345</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1771</v>
+        <v>342</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>8</v>
+        <v>266</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>347</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>52</v>
+        <v>342</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>56</v>
+        <v>348</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>57</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>58</v>
+        <v>350</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>342</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1775</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>61</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>62</v>
+        <v>409</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>52</v>
+        <v>410</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>19</v>
+        <v>411</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>64</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>65</v>
+        <v>413</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>66</v>
+        <v>410</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>8</v>
+        <v>414</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>68</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>639</v>
+        <v>416</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1794</v>
+        <v>410</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>8</v>
+        <v>417</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>320</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>69</v>
+        <v>419</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>70</v>
+        <v>410</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1770</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>71</v>
+        <v>420</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>73</v>
+        <v>313</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1791</v>
+        <v>314</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>74</v>
+        <v>300</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="6">
-        <v>1799</v>
+        <v>314</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>8</v>
+        <v>317</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>77</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>78</v>
+      <c r="A27" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>82</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>83</v>
+      <c r="A28" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>85</v>
+        <v>309</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>86</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>88</v>
+      <c r="A29" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>91</v>
+      <c r="A30" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>94</v>
+      <c r="A31" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" s="9">
+        <v>1726</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>96</v>
+      <c r="A32" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
-        <v>640</v>
+        <v>471</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1769</v>
+        <v>638</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>472</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>320</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>167</v>
+        <v>474</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>92</v>
+        <v>638</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>98</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>99</v>
+      <c r="A35" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>92</v>
+        <v>638</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>100</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C37" s="6">
+        <v>1789</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="B38" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>113</v>
+      <c r="C39" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>110</v>
+      <c r="A40" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>109</v>
+      <c r="A41" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>107</v>
+      <c r="A42" s="4" t="s">
+        <v>515</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>103</v>
+        <v>516</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>105</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>101</v>
+      <c r="A43" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>130</v>
+      <c r="A44" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>131</v>
+      <c r="A45" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>127</v>
+        <v>376</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>133</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>135</v>
+      <c r="A46" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>127</v>
+      <c r="A47" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>639</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>139</v>
+      <c r="A48" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>639</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>139</v>
+        <v>79</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>639</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>145</v>
+      <c r="A50" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>139</v>
+        <v>387</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>147</v>
+        <v>384</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>148</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>149</v>
+      <c r="A51" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>139</v>
+        <v>387</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>26</v>
+        <v>390</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>85</v>
+        <v>384</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>150</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>151</v>
+      <c r="A52" s="4" t="s">
+        <v>391</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>152</v>
+        <v>387</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>153</v>
+        <v>392</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>154</v>
+        <v>384</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>155</v>
+        <v>393</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="4" t="s">
-        <v>156</v>
+        <v>277</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>157</v>
+        <v>273</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1783</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>160</v>
-      </c>
       <c r="E54" s="5" t="s">
-        <v>161</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>168</v>
+        <v>280</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>152</v>
+        <v>273</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D55" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D55" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>174</v>
+      <c r="D56" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>178</v>
+      <c r="A57" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>181</v>
+      <c r="A58" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>183</v>
+      <c r="A59" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C59" s="9">
+        <v>1783</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>184</v>
+      <c r="A60" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>188</v>
+        <v>574</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>189</v>
+        <v>21</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1750</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>190</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>194</v>
+      <c r="A62" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>195</v>
+      <c r="A63" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>196</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>201</v>
+      <c r="A64" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>202</v>
+      <c r="A65" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>198</v>
+        <v>484</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>200</v>
+        <v>485</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>204</v>
+        <v>486</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>205</v>
+      <c r="A66" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>198</v>
+        <v>484</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>206</v>
+        <v>487</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>207</v>
+        <v>488</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>231</v>
+      <c r="A70" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>216</v>
+      <c r="A73" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>212</v>
+      <c r="A74" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>34</v>
+        <v>259</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>260</v>
@@ -3724,2256 +3744,2274 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" s="5" t="s">
+      <c r="A78" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>253</v>
       </c>
+      <c r="C78" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>251</v>
+      <c r="A79" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>248</v>
+      <c r="A80" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>246</v>
+      <c r="A81" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>243</v>
+      <c r="A82" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>239</v>
+      <c r="A83" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>271</v>
+      <c r="A84" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>272</v>
+        <v>209</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>279</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>281</v>
+        <v>70</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>283</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>284</v>
+        <v>556</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>285</v>
+        <v>437</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>286</v>
+        <v>439</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>240</v>
+        <v>557</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>287</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>288</v>
+        <v>558</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>285</v>
+        <v>437</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>14</v>
+        <v>535</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>19</v>
+        <v>559</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>289</v>
+        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>290</v>
+        <v>561</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>285</v>
+        <v>437</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>291</v>
+        <v>535</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>292</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>294</v>
+      <c r="A91" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C92" s="6">
-        <v>1783</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>300</v>
+      <c r="A92" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D93" s="5" t="s">
+      <c r="A93" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E95" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" s="9">
+        <v>1794</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="8" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D94" t="s">
-        <v>303</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>313</v>
+      <c r="A97" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>315</v>
+      <c r="A98" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C98" s="9">
+        <v>1791</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>320</v>
+      <c r="A99" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C99" s="9">
+        <v>1799</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>327</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>13</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>329</v>
+        <v>6</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>254</v>
+        <v>14</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>330</v>
+        <v>15</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>331</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4" t="s">
-        <v>332</v>
+        <v>572</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>329</v>
+        <v>6</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>333</v>
+        <v>7</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>335</v>
+        <v>573</v>
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>337</v>
+      <c r="A104" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4" t="s">
-        <v>338</v>
+        <v>157</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>340</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>152</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>342</v>
+        <v>8</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>343</v>
+        <v>86</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4" t="s">
-        <v>344</v>
+        <v>579</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>345</v>
+        <v>82</v>
+      </c>
+      <c r="C107" s="6">
+        <v>1769</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>346</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>347</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>155</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>349</v>
+        <v>87</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>350</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="4" t="s">
-        <v>351</v>
+      <c r="A109" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>282</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>353</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
-        <v>354</v>
+        <v>478</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>355</v>
+        <v>479</v>
+      </c>
+      <c r="C110" s="6">
+        <v>1721</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>282</v>
+        <v>36</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>356</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>360</v>
+      <c r="A111" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C111" s="9">
+        <v>1748</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C112" s="6">
-        <v>1783</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>363</v>
+      <c r="A112" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="4" t="s">
-        <v>364</v>
+        <v>489</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>365</v>
+        <v>490</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>366</v>
+        <v>491</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="4" t="s">
-        <v>367</v>
+        <v>492</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>365</v>
+        <v>490</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>8</v>
+        <v>493</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>320</v>
+        <v>494</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="4" t="s">
-        <v>368</v>
+        <v>48</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="C115" s="6">
-        <v>1772</v>
+        <v>49</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
-        <v>370</v>
+        <v>578</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>176</v>
+        <v>49</v>
+      </c>
+      <c r="C116" s="6">
+        <v>1771</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>282</v>
+        <v>8</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>371</v>
+        <v>297</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="4" t="s">
-        <v>372</v>
+        <v>52</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>373</v>
+        <v>49</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>374</v>
+        <v>8</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>375</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>377</v>
+      <c r="A118" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="4" t="s">
-        <v>378</v>
+        <v>58</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>373</v>
+        <v>49</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>379</v>
+        <v>59</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>323</v>
+        <v>18</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>380</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="4" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C120" s="6">
-        <v>1775</v>
+        <v>368</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="4" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>385</v>
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>372</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="4" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>388</v>
+        <v>163</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>147</v>
+        <v>372</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="4" t="s">
-        <v>390</v>
+        <v>33</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>383</v>
+        <v>34</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>391</v>
+        <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="4" t="s">
-        <v>392</v>
+        <v>38</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>383</v>
+        <v>34</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>388</v>
+        <v>39</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>229</v>
+        <v>8</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>393</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="4" t="s">
-        <v>394</v>
+        <v>41</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>395</v>
+        <v>34</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>396</v>
+        <v>42</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>397</v>
+        <v>31</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>398</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="4" t="s">
-        <v>399</v>
+        <v>576</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>93</v>
+        <v>34</v>
+      </c>
+      <c r="C126" s="6">
+        <v>1769</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>401</v>
+        <v>577</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="4" t="s">
-        <v>402</v>
+        <v>44</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>403</v>
+        <v>34</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>404</v>
+        <v>45</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>323</v>
+        <v>46</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>405</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="4" t="s">
-        <v>406</v>
+      <c r="A128" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>403</v>
+        <v>93</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D128" t="s">
-        <v>407</v>
+        <v>100</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>408</v>
+        <v>99</v>
       </c>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="4" t="s">
-        <v>409</v>
+      <c r="A129" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>403</v>
+        <v>93</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>407</v>
+        <v>71</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>410</v>
+        <v>97</v>
       </c>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="4" t="s">
-        <v>411</v>
+      <c r="A130" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>413</v>
+        <v>95</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>414</v>
+        <v>71</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>415</v>
+        <v>94</v>
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>419</v>
+      <c r="A131" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>422</v>
+      <c r="A132" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="4" t="s">
-        <v>423</v>
+      <c r="A133" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>424</v>
+        <v>184</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>421</v>
+        <v>186</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>425</v>
+        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="4" t="s">
-        <v>426</v>
+      <c r="A134" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>424</v>
+        <v>184</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>427</v>
+        <v>192</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>421</v>
+        <v>135</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>415</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="4" t="s">
-        <v>428</v>
+      <c r="A135" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>424</v>
+        <v>184</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>429</v>
+        <v>195</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>421</v>
+        <v>196</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>430</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>434</v>
+      <c r="A136" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="4" t="s">
-        <v>435</v>
+      <c r="A137" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>432</v>
+        <v>227</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>436</v>
+        <v>230</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>421</v>
+        <v>226</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>437</v>
+        <v>229</v>
       </c>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="4" t="s">
-        <v>438</v>
+      <c r="A138" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>432</v>
+        <v>227</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>439</v>
+        <v>35</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>421</v>
+        <v>226</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>440</v>
+        <v>225</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="4" t="s">
-        <v>441</v>
+        <v>518</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>442</v>
+        <v>519</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>244</v>
+        <v>520</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>443</v>
+        <v>8</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>444</v>
+        <v>521</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="4" t="s">
-        <v>445</v>
+        <v>522</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>442</v>
+        <v>519</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>176</v>
+        <v>308</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>443</v>
+        <v>71</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>320</v>
+        <v>523</v>
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>447</v>
+      <c r="A141" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>451</v>
+      <c r="A142" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>454</v>
+      <c r="A143" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>457</v>
+      <c r="A144" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="4" t="s">
-        <v>458</v>
+      <c r="A145" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C145" s="6">
-        <v>1770</v>
+        <v>140</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>459</v>
+        <v>142</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>320</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="4" t="s">
-        <v>460</v>
+        <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>462</v>
+        <v>145</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>463</v>
+        <v>8</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>464</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="4" t="s">
-        <v>465</v>
+      <c r="A147" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>462</v>
+        <v>92</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>240</v>
+        <v>148</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>466</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
-        <v>467</v>
+        <v>156</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>468</v>
+        <v>140</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>469</v>
+        <v>150</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>470</v>
+        <v>36</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>471</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="4" t="s">
-        <v>472</v>
+      <c r="A149" s="5" t="s">
+        <v>541</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C149" s="6">
-        <v>1789</v>
+        <v>450</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>542</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>34</v>
+        <v>451</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>473</v>
+        <v>543</v>
       </c>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="4" t="s">
-        <v>474</v>
+      <c r="A150" s="5" t="s">
+        <v>544</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>477</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="4" t="s">
-        <v>478</v>
+      <c r="A151" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>106</v>
+        <v>535</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>479</v>
+        <v>548</v>
       </c>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="5" t="s">
-        <v>581</v>
+      <c r="A152" s="4" t="s">
+        <v>453</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>582</v>
+        <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>583</v>
+        <v>455</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="5" t="s">
-        <v>584</v>
+      <c r="A153" s="4" t="s">
+        <v>457</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>585</v>
+        <v>455</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>586</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="5" t="s">
-        <v>587</v>
+      <c r="A154" s="4" t="s">
+        <v>334</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>487</v>
+        <v>335</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>588</v>
+        <v>8</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>589</v>
+        <v>336</v>
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="5" t="s">
-        <v>590</v>
+      <c r="A155" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>487</v>
+        <v>335</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>591</v>
+        <v>100</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>489</v>
+        <v>8</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>592</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>594</v>
+      <c r="A156" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C156" s="9">
+        <v>1772</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="5" t="s">
-        <v>595</v>
+      <c r="A157" s="4" t="s">
+        <v>339</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>490</v>
+        <v>335</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>596</v>
+        <v>163</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>491</v>
+        <v>266</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>492</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>597</v>
+        <v>526</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>591</v>
+        <v>527</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>598</v>
+        <v>445</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>599</v>
+        <v>529</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>596</v>
+        <v>39</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>600</v>
+        <v>531</v>
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="E160" s="5" t="s">
-        <v>603</v>
+      <c r="A160" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>604</v>
+        <v>534</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>70</v>
+        <v>535</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>605</v>
+        <v>536</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>606</v>
+        <v>114</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>493</v>
+        <v>104</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>591</v>
+        <v>113</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>607</v>
+        <v>112</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>608</v>
+        <v>111</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>609</v>
+        <v>110</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>495</v>
+        <v>104</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>610</v>
+        <v>109</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>611</v>
+        <v>8</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>612</v>
+        <v>108</v>
       </c>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="5" t="s">
-        <v>613</v>
+      <c r="A164" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>495</v>
+        <v>104</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>591</v>
+        <v>30</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>614</v>
+        <v>107</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>615</v>
+        <v>106</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>616</v>
+        <v>105</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>480</v>
+        <v>104</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>482</v>
+        <v>103</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>617</v>
+        <v>8</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>481</v>
+        <v>102</v>
       </c>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="5" t="s">
-        <v>618</v>
+      <c r="A166" s="4" t="s">
+        <v>459</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>591</v>
+        <v>460</v>
+      </c>
+      <c r="C166" s="6">
+        <v>1760</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>619</v>
+        <v>461</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>620</v>
+        <v>462</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>621</v>
+        <v>549</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>591</v>
+        <v>550</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>614</v>
+        <v>551</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>622</v>
+        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>623</v>
+        <v>553</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>186</v>
+        <v>535</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>483</v>
+        <v>554</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>624</v>
+        <v>555</v>
       </c>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="5" t="s">
-        <v>625</v>
+      <c r="A169" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>591</v>
+        <v>465</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>585</v>
+        <v>36</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="5" t="s">
-        <v>626</v>
+      <c r="A170" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>591</v>
+        <v>464</v>
+      </c>
+      <c r="C170" s="6">
+        <v>1710</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>585</v>
+        <v>8</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>627</v>
+        <v>468</v>
       </c>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>629</v>
+      <c r="A171" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>631</v>
+      <c r="A172" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="4" t="s">
-        <v>496</v>
+        <v>285</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>497</v>
+        <v>282</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>14</v>
+        <v>286</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>498</v>
+        <v>287</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>499</v>
+        <v>288</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="4" t="s">
-        <v>500</v>
+        <v>289</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>497</v>
+        <v>282</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>498</v>
+        <v>283</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>501</v>
+        <v>290</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="4" t="s">
-        <v>502</v>
+        <v>291</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C175" s="6">
-        <v>1760</v>
+        <v>282</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>504</v>
+        <v>287</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>505</v>
+        <v>292</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
-        <v>506</v>
+        <v>304</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>507</v>
+        <v>305</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>508</v>
+        <v>239</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>509</v>
+        <v>307</v>
       </c>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="C177" s="6">
-        <v>1710</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>511</v>
+      <c r="A177" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="4" t="s">
-        <v>512</v>
+        <v>311</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>507</v>
+        <v>305</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>513</v>
+        <v>134</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>514</v>
+        <v>312</v>
       </c>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="4" t="s">
-        <v>515</v>
+      <c r="A179" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>516</v>
+        <v>234</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>517</v>
+        <v>243</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>518</v>
+        <v>241</v>
       </c>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="4" t="s">
-        <v>519</v>
+      <c r="A180" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>516</v>
+        <v>234</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>520</v>
+        <v>238</v>
       </c>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="4" t="s">
-        <v>521</v>
+      <c r="A181" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>516</v>
+        <v>234</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>522</v>
+        <v>236</v>
       </c>
     </row>
     <row r="182" spans="1:5">
-      <c r="A182" s="4" t="s">
-        <v>523</v>
+      <c r="A182" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="C182" s="6">
-        <v>1721</v>
+        <v>234</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>525</v>
+        <v>233</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="4" t="s">
-        <v>526</v>
+        <v>293</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>524</v>
+        <v>294</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>527</v>
+        <v>295</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>528</v>
+        <v>296</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>529</v>
+        <v>297</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
-        <v>530</v>
+        <v>298</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>524</v>
+        <v>294</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>531</v>
+        <v>301</v>
       </c>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>535</v>
+      <c r="A185" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="4" t="s">
-        <v>532</v>
+      <c r="A186" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>533</v>
+        <v>159</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>536</v>
+        <v>160</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>537</v>
+        <v>161</v>
       </c>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="4" t="s">
-        <v>538</v>
+      <c r="A187" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>539</v>
+        <v>159</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>540</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="4" t="s">
-        <v>541</v>
+      <c r="A188" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>539</v>
+        <v>159</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>542</v>
+        <v>75</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>543</v>
+        <v>168</v>
       </c>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="4" t="s">
-        <v>544</v>
+      <c r="A189" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>546</v>
+        <v>170</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="4" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>545</v>
+        <v>395</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>80</v>
+        <v>396</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>548</v>
+        <v>397</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>549</v>
+        <v>398</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>545</v>
+        <v>395</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>550</v>
+        <v>399</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>551</v>
+        <v>384</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>552</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="4" t="s">
-        <v>553</v>
+        <v>401</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>554</v>
+        <v>395</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>186</v>
+        <v>402</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>200</v>
+        <v>384</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>555</v>
+        <v>403</v>
       </c>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="4" t="s">
-        <v>556</v>
+      <c r="A193" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>554</v>
+        <v>127</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>213</v>
+        <v>75</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>557</v>
+        <v>129</v>
       </c>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="4" t="s">
-        <v>558</v>
+      <c r="A194" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>554</v>
+        <v>127</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>213</v>
+        <v>75</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>559</v>
+        <v>132</v>
       </c>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="4" t="s">
-        <v>560</v>
+      <c r="A195" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>561</v>
+        <v>127</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>562</v>
+        <v>136</v>
       </c>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="B196" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D196" s="5" t="s">
+      <c r="B200" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E200" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="E196" s="5" t="s">
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="5" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E199" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="D200" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E200" s="5" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" s="4" t="s">
-        <v>578</v>
-      </c>
       <c r="B201" s="5" t="s">
-        <v>573</v>
+        <v>441</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>87</v>
+        <v>535</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>580</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E201">
+    <sortCondition ref="B2:B201"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{01BEB8B3-FA8A-46D2-A3F2-A16DDC5DC041}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{8846CFE6-B6DD-444B-BA27-DE9118EFA98F}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{632107C4-0CA6-4716-AF0C-9917625D9347}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{546B8D2D-6935-4CFE-A108-C653923A76FA}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{1177A6F2-E6B2-476E-A2A6-B0E82CDAA77D}"/>
-    <hyperlink ref="A10" r:id="rId7" xr:uid="{EA46CCD8-B590-4A96-8E08-7366BE83116E}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{AAF38FFF-A3E8-4173-A180-4DB72AED057B}"/>
-    <hyperlink ref="A12" r:id="rId9" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A13" r:id="rId10" xr:uid="{35E3E0C5-7760-4EB4-A63D-8DC2B45AB000}"/>
-    <hyperlink ref="A14" r:id="rId11" xr:uid="{AA3677AF-F09C-418C-BA66-01C1E134A694}"/>
-    <hyperlink ref="A16" r:id="rId12" xr:uid="{EE8CD801-4C81-44EB-A625-9BD03F98AE32}"/>
-    <hyperlink ref="A17" r:id="rId13" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A19" r:id="rId14" xr:uid="{E16F0F03-CFFD-42C7-A057-4946BCDB4EC0}"/>
-    <hyperlink ref="A20" r:id="rId15" xr:uid="{57E8F42C-59D9-4C9C-989B-9C901F6F0607}"/>
-    <hyperlink ref="A21" r:id="rId16" xr:uid="{251BF111-7C01-4C51-B32A-BDBEEDC7FE67}"/>
-    <hyperlink ref="A22" r:id="rId17" xr:uid="{050A610E-B724-4EF6-A305-61DFFF57E08C}"/>
-    <hyperlink ref="A24" r:id="rId18" xr:uid="{2AD7A5BE-2C7A-40C2-93EC-D2CF39349072}"/>
-    <hyperlink ref="A25" r:id="rId19" xr:uid="{55C74D6C-00EA-4A8A-AFE5-A2C94B37F873}"/>
-    <hyperlink ref="A26" r:id="rId20" xr:uid="{53546570-11DB-4F86-BA78-DB01E4175359}"/>
-    <hyperlink ref="A53" r:id="rId21" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A32" r:id="rId22" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A38" r:id="rId23" xr:uid="{35843622-C449-41E5-858B-122E86FE5585}"/>
-    <hyperlink ref="A47" r:id="rId24" xr:uid="{576FD0EA-8E95-4DD9-9DE2-D6D386132173}"/>
-    <hyperlink ref="A34" r:id="rId25" xr:uid="{FECCE726-C931-490B-A82B-00D49DAE2D1A}"/>
-    <hyperlink ref="A55" r:id="rId26" xr:uid="{B4CACE6B-4585-40BF-9570-7E775FC2373D}"/>
-    <hyperlink ref="A46" r:id="rId27" xr:uid="{68A68607-7EA8-4768-B5B9-A112A4C6A9EF}"/>
-    <hyperlink ref="A31" r:id="rId28" xr:uid="{8A76ADFE-8287-4A33-8D3C-7E7D0281B24E}"/>
-    <hyperlink ref="A61" r:id="rId29" xr:uid="{69DF61A4-652A-4BEC-9D5E-20122E52140C}"/>
-    <hyperlink ref="A93" r:id="rId30" xr:uid="{A706DABA-E5F6-4965-92B2-0B4D8EECE9A9}"/>
-    <hyperlink ref="A92" r:id="rId31" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A94" r:id="rId32" xr:uid="{28DCFBA1-50BA-44D0-B4C1-3DCB2A899994}"/>
-    <hyperlink ref="A200" r:id="rId33" xr:uid="{6FEB838B-F605-42FF-BEC0-808745C25F46}"/>
-    <hyperlink ref="A199" r:id="rId34" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
-    <hyperlink ref="A198" r:id="rId35" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
-    <hyperlink ref="A195" r:id="rId36" xr:uid="{2562AA1A-2ED2-41BE-A099-5101BB438FB5}"/>
-    <hyperlink ref="A197" r:id="rId37" xr:uid="{882D1A12-D43F-4228-8FB4-8D41404A522E}"/>
-    <hyperlink ref="A196" r:id="rId38" xr:uid="{74D8508D-C02B-4460-BF7F-39F813F17B83}"/>
-    <hyperlink ref="A201" r:id="rId39" xr:uid="{3BE9722A-5485-40E0-8AD1-CFF5E7F9C89B}"/>
-    <hyperlink ref="A194" r:id="rId40" xr:uid="{6052EA8F-A06C-4030-B911-93D5F34BB1AB}"/>
-    <hyperlink ref="A193" r:id="rId41" xr:uid="{5050CD76-E020-42D7-8372-6A028F57267B}"/>
-    <hyperlink ref="A192" r:id="rId42" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
-    <hyperlink ref="A191" r:id="rId43" xr:uid="{2D892170-F3ED-462C-A0E6-BF99CECAEBAD}"/>
-    <hyperlink ref="A190" r:id="rId44" xr:uid="{E47B0A35-D6A5-46B2-9EAE-BB4961F5EEED}"/>
-    <hyperlink ref="A189" r:id="rId45" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A187" r:id="rId46" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A188" r:id="rId47" xr:uid="{ADA8E203-9BC6-4247-8126-40DD148927E8}"/>
-    <hyperlink ref="A186" r:id="rId48" xr:uid="{244B0B97-E64F-48EE-8997-BE484716E578}"/>
-    <hyperlink ref="A185" r:id="rId49" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
-    <hyperlink ref="A176" r:id="rId50" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A178" r:id="rId51" xr:uid="{4E1E143B-6B94-4D11-A72D-138A79AA7631}"/>
-    <hyperlink ref="A177" r:id="rId52" xr:uid="{C00F019D-685D-4B14-981E-47081DD2F058}"/>
-    <hyperlink ref="A179" r:id="rId53" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A180" r:id="rId54" xr:uid="{F9DC5954-BBFC-4D2C-A9D5-F511742D050E}"/>
-    <hyperlink ref="A181" r:id="rId55" xr:uid="{F271E2E7-24F4-4198-BC26-73393C3369D5}"/>
-    <hyperlink ref="A184" r:id="rId56" xr:uid="{304DE42C-BAC1-491E-9B13-744585EAFA1D}"/>
-    <hyperlink ref="A183" r:id="rId57" xr:uid="{168F4258-4124-47A7-A106-FC3FC700BF45}"/>
-    <hyperlink ref="A182" r:id="rId58" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A175" r:id="rId59" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
-    <hyperlink ref="A173" r:id="rId60" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
-    <hyperlink ref="A174" r:id="rId61" xr:uid="{E768E684-8D4F-4A90-9C29-53B564F3AEEE}"/>
-    <hyperlink ref="A148" r:id="rId62" xr:uid="{87E30B9A-02F8-462A-8B4A-D7A9E1F6EB99}"/>
-    <hyperlink ref="A149" r:id="rId63" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
-    <hyperlink ref="A150" r:id="rId64" xr:uid="{393B41FC-3B90-4000-8910-1F773A2C2244}"/>
-    <hyperlink ref="A151" r:id="rId65" xr:uid="{A4967510-4B31-45B5-A9EF-9DF2BC4D2F52}"/>
-    <hyperlink ref="A109" r:id="rId66" xr:uid="{4FFEF3FA-A758-444F-A755-C3C1C569C014}"/>
-    <hyperlink ref="A110" r:id="rId67" xr:uid="{1FBED728-5E07-4620-8247-84B0CA72DFA2}"/>
-    <hyperlink ref="A111" r:id="rId68" xr:uid="{313043B5-CA81-430B-8E03-2D78B06D9D84}"/>
-    <hyperlink ref="A112" r:id="rId69" xr:uid="{77EB64B3-F9E4-4DA7-BB3D-372AA5009B32}"/>
-    <hyperlink ref="A130" r:id="rId70" xr:uid="{E4618BD0-2243-40D4-832A-471238C9525D}"/>
-    <hyperlink ref="A131" r:id="rId71" xr:uid="{322679B8-723C-41F6-845D-AF1D56A55B6D}"/>
-    <hyperlink ref="A132" r:id="rId72" display="https://upload.wikimedia.org/wikipedia/commons/e/e8/Dmitry_Levitsky_-_%D0%9F%D0%BE%D1%80%D1%82%D1%80%D0%B5%D1%82_%D0%9C.%D0%90.%D0%94%D1%8C%D1%8F%D0%BA%D0%BE%D0%B2%D0%BE%D0%B9_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{423F91D2-34B4-4D68-AE3C-F51AE35E6DBD}"/>
-    <hyperlink ref="A125" r:id="rId73" xr:uid="{8617592A-0D68-45CD-9E0E-E1DF6D1ED620}"/>
-    <hyperlink ref="A126" r:id="rId74" xr:uid="{FCB01430-72BF-469A-9077-75F553B76135}"/>
-    <hyperlink ref="A127" r:id="rId75" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
-    <hyperlink ref="A128" r:id="rId76" xr:uid="{498C856B-1FBB-43D0-AC72-2E0AF7437ADF}"/>
-    <hyperlink ref="A129" r:id="rId77" xr:uid="{56B02F73-2F13-45B7-976D-964954E8F279}"/>
-    <hyperlink ref="A135" r:id="rId78" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
-    <hyperlink ref="A134" r:id="rId79" xr:uid="{D489065C-0363-4F65-A97E-78D9D1F1CE27}"/>
-    <hyperlink ref="A133" r:id="rId80" xr:uid="{BD93FEB8-E724-420B-A83E-2061ED37CAF2}"/>
-    <hyperlink ref="A137" r:id="rId81" xr:uid="{5D4CB707-D9DF-4336-8079-9A08746A0C3E}"/>
-    <hyperlink ref="A138" r:id="rId82" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
-    <hyperlink ref="A136" r:id="rId83" xr:uid="{96A16812-ED9B-4799-9AFA-DFA51BC408DA}"/>
-    <hyperlink ref="A139" r:id="rId84" xr:uid="{2D23B342-C714-4EF3-BBB2-0A8B3A4B5564}"/>
-    <hyperlink ref="A140" r:id="rId85" location="/media/File:Sj%C3%A4lvportr%C3%A4tt_(Alexander_Roslin)_-_Nationalmuseum_-_44990.tif" xr:uid="{58A93415-F4B8-475B-9925-A92EE34A2CAB}"/>
-    <hyperlink ref="A141" r:id="rId86" xr:uid="{22C5138C-1293-437E-BD1A-D48C932D0D04}"/>
-    <hyperlink ref="A142" r:id="rId87" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
-    <hyperlink ref="A143" r:id="rId88" xr:uid="{5009CD0A-CBCD-41D4-9A4E-8F0A1F817F5C}"/>
-    <hyperlink ref="A144" r:id="rId89" xr:uid="{71D24384-8BF3-443A-B910-7029D965CC2C}"/>
-    <hyperlink ref="A145" r:id="rId90" xr:uid="{A80791BD-384F-4940-BF55-05DE4D7D59D5}"/>
-    <hyperlink ref="A146" r:id="rId91" xr:uid="{F42374B4-D3A7-4EBD-A8FF-2BB134B8D437}"/>
-    <hyperlink ref="A147" r:id="rId92" xr:uid="{5B3E406C-63A9-450F-B240-A491C4A9C86A}"/>
-    <hyperlink ref="A113" r:id="rId93" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A114" r:id="rId94" xr:uid="{18FB7F9C-C3F5-4CA1-8C00-F365ABE9E7B0}"/>
-    <hyperlink ref="A115" r:id="rId95" xr:uid="{9FD4CFDD-AC06-4D03-9227-C2253940B047}"/>
-    <hyperlink ref="A116" r:id="rId96" xr:uid="{16BCB221-1B61-49E4-80D9-7D3BC0B74CD9}"/>
-    <hyperlink ref="A117" r:id="rId97" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A118" r:id="rId98" xr:uid="{7494B6B1-F895-4BD2-966C-FDEEEE6175C6}"/>
-    <hyperlink ref="A119" r:id="rId99" xr:uid="{A7225E7F-C594-4B8B-8385-A0ACE1A92F05}"/>
-    <hyperlink ref="A120" r:id="rId100" xr:uid="{23FE1FF8-50DC-4797-B753-2EE5C1C9B47F}"/>
-    <hyperlink ref="A121" r:id="rId101" xr:uid="{9608CD97-2B71-4393-BBDE-35018F637ED3}"/>
-    <hyperlink ref="A122" r:id="rId102" location="/media/File:Henry_Fuseli_-_Titania_and_Bottom.jpg" xr:uid="{0030181B-0CE3-4A45-8762-B92E786D84F7}"/>
-    <hyperlink ref="A123" r:id="rId103" xr:uid="{81061E2E-6D55-49E7-83CF-6577EEE70E1C}"/>
-    <hyperlink ref="A124" r:id="rId104" xr:uid="{0F84B4F2-940C-42B6-9B56-733A4FFAD50C}"/>
-    <hyperlink ref="A105" r:id="rId105" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A106" r:id="rId106" xr:uid="{F5BE76AF-7994-4D97-B432-4450F54C3EC3}"/>
-    <hyperlink ref="A107" r:id="rId107" xr:uid="{14702591-FF74-4F77-A775-FC02CDD017BD}"/>
-    <hyperlink ref="A108" r:id="rId108" xr:uid="{E23A852A-F418-4045-8287-B06A43F84279}"/>
-    <hyperlink ref="A95" r:id="rId109" xr:uid="{4AF5ADFF-1ADB-4C17-969C-DB8FB9AA6271}"/>
-    <hyperlink ref="A96" r:id="rId110" xr:uid="{3FD70B98-7E3D-468D-913D-77ADE4B6D096}"/>
-    <hyperlink ref="A97" r:id="rId111" xr:uid="{14279E30-A53D-4169-A916-9899A72B4335}"/>
-    <hyperlink ref="A98" r:id="rId112" xr:uid="{5B810F6E-1BAC-40EE-9B9B-16BEC438586F}"/>
-    <hyperlink ref="A99" r:id="rId113" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A101" r:id="rId114" xr:uid="{0EF1476F-2591-4609-BBBC-5E3F94F991D7}"/>
-    <hyperlink ref="A100" r:id="rId115" xr:uid="{3D67F0ED-B33C-4C7E-B393-51A347B64C72}"/>
-    <hyperlink ref="A102" r:id="rId116" xr:uid="{2D77DE26-68EF-4E17-A593-9E1F611357DF}"/>
-    <hyperlink ref="A104" r:id="rId117" xr:uid="{A425E694-3572-4822-A8BF-CE69E8D101B1}"/>
-    <hyperlink ref="A103" r:id="rId118" xr:uid="{D41BE3A6-CFDA-4DD2-BE2D-40A241CB5ECA}"/>
-    <hyperlink ref="A5" r:id="rId119" xr:uid="{5EF5C1A5-93E3-4292-9E80-3BA88C2778FF}"/>
-    <hyperlink ref="A8" r:id="rId120" xr:uid="{B8FA5090-B2AC-4000-946F-4F8E9F976ABB}"/>
-    <hyperlink ref="A15" r:id="rId121" xr:uid="{33892484-7CC4-4409-83EE-5B8494713305}"/>
-    <hyperlink ref="A18" r:id="rId122" xr:uid="{C8CC2851-6618-4C92-9F7B-F36AF03A62D5}"/>
-    <hyperlink ref="A23" r:id="rId123" xr:uid="{B5B73C81-18A7-480B-AE84-A5417EC2DFCD}"/>
-    <hyperlink ref="A33" r:id="rId124" xr:uid="{BD9F090B-F993-424A-9D4E-643835A4A1B5}"/>
-    <hyperlink ref="A29" r:id="rId125" xr:uid="{789A0F0B-83F5-44B2-8AF4-E63C03129061}"/>
+    <hyperlink ref="A100" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
+    <hyperlink ref="A101" r:id="rId2" xr:uid="{01BEB8B3-FA8A-46D2-A3F2-A16DDC5DC041}"/>
+    <hyperlink ref="A102" r:id="rId3" xr:uid="{632107C4-0CA6-4716-AF0C-9917625D9347}"/>
+    <hyperlink ref="A60" r:id="rId4" xr:uid="{546B8D2D-6935-4CFE-A108-C653923A76FA}"/>
+    <hyperlink ref="A63" r:id="rId5" xr:uid="{EA46CCD8-B590-4A96-8E08-7366BE83116E}"/>
+    <hyperlink ref="A123" r:id="rId6" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A124" r:id="rId7" xr:uid="{35E3E0C5-7760-4EB4-A63D-8DC2B45AB000}"/>
+    <hyperlink ref="A125" r:id="rId8" xr:uid="{AA3677AF-F09C-418C-BA66-01C1E134A694}"/>
+    <hyperlink ref="A127" r:id="rId9" xr:uid="{EE8CD801-4C81-44EB-A625-9BD03F98AE32}"/>
+    <hyperlink ref="A115" r:id="rId10" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A117" r:id="rId11" xr:uid="{E16F0F03-CFFD-42C7-A057-4946BCDB4EC0}"/>
+    <hyperlink ref="A119" r:id="rId12" xr:uid="{251BF111-7C01-4C51-B32A-BDBEEDC7FE67}"/>
+    <hyperlink ref="A146" r:id="rId13" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A106" r:id="rId14" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A164" r:id="rId15" xr:uid="{35843622-C449-41E5-858B-122E86FE5585}"/>
+    <hyperlink ref="A41" r:id="rId16" xr:uid="{576FD0EA-8E95-4DD9-9DE2-D6D386132173}"/>
+    <hyperlink ref="A108" r:id="rId17" xr:uid="{FECCE726-C931-490B-A82B-00D49DAE2D1A}"/>
+    <hyperlink ref="A148" r:id="rId18" xr:uid="{B4CACE6B-4585-40BF-9570-7E775FC2373D}"/>
+    <hyperlink ref="A105" r:id="rId19" xr:uid="{8A76ADFE-8287-4A33-8D3C-7E7D0281B24E}"/>
+    <hyperlink ref="A70" r:id="rId20" xr:uid="{69DF61A4-652A-4BEC-9D5E-20122E52140C}"/>
+    <hyperlink ref="A54" r:id="rId21" xr:uid="{A706DABA-E5F6-4965-92B2-0B4D8EECE9A9}"/>
+    <hyperlink ref="A53" r:id="rId22" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A55" r:id="rId23" xr:uid="{28DCFBA1-50BA-44D0-B4C1-3DCB2A899994}"/>
+    <hyperlink ref="A140" r:id="rId24" xr:uid="{6FEB838B-F605-42FF-BEC0-808745C25F46}"/>
+    <hyperlink ref="A139" r:id="rId25" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
+    <hyperlink ref="A42" r:id="rId26" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
+    <hyperlink ref="A10" r:id="rId27" xr:uid="{6052EA8F-A06C-4030-B911-93D5F34BB1AB}"/>
+    <hyperlink ref="A9" r:id="rId28" xr:uid="{5050CD76-E020-42D7-8372-6A028F57267B}"/>
+    <hyperlink ref="A8" r:id="rId29" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
+    <hyperlink ref="A4" r:id="rId30" xr:uid="{2D892170-F3ED-462C-A0E6-BF99CECAEBAD}"/>
+    <hyperlink ref="A2" r:id="rId31" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A113" r:id="rId32" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A114" r:id="rId33" xr:uid="{ADA8E203-9BC6-4247-8126-40DD148927E8}"/>
+    <hyperlink ref="A66" r:id="rId34" xr:uid="{244B0B97-E64F-48EE-8997-BE484716E578}"/>
+    <hyperlink ref="A65" r:id="rId35" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
+    <hyperlink ref="A169" r:id="rId36" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A170" r:id="rId37" xr:uid="{C00F019D-685D-4B14-981E-47081DD2F058}"/>
+    <hyperlink ref="A33" r:id="rId38" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A34" r:id="rId39" xr:uid="{F9DC5954-BBFC-4D2C-A9D5-F511742D050E}"/>
+    <hyperlink ref="A35" r:id="rId40" xr:uid="{F271E2E7-24F4-4198-BC26-73393C3369D5}"/>
+    <hyperlink ref="A110" r:id="rId41" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A166" r:id="rId42" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
+    <hyperlink ref="A152" r:id="rId43" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
+    <hyperlink ref="A153" r:id="rId44" xr:uid="{E768E684-8D4F-4A90-9C29-53B564F3AEEE}"/>
+    <hyperlink ref="A37" r:id="rId45" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
+    <hyperlink ref="A80" r:id="rId46" xr:uid="{A4967510-4B31-45B5-A9EF-9DF2BC4D2F52}"/>
+    <hyperlink ref="A45" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/e/e8/Dmitry_Levitsky_-_%D0%9F%D0%BE%D1%80%D1%82%D1%80%D0%B5%D1%82_%D0%9C.%D0%90.%D0%94%D1%8C%D1%8F%D0%BA%D0%BE%D0%B2%D0%BE%D0%B9_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{423F91D2-34B4-4D68-AE3C-F51AE35E6DBD}"/>
+    <hyperlink ref="A15" r:id="rId48" xr:uid="{8617592A-0D68-45CD-9E0E-E1DF6D1ED620}"/>
+    <hyperlink ref="A16" r:id="rId49" xr:uid="{FCB01430-72BF-469A-9077-75F553B76135}"/>
+    <hyperlink ref="A120" r:id="rId50" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
+    <hyperlink ref="A121" r:id="rId51" xr:uid="{498C856B-1FBB-43D0-AC72-2E0AF7437ADF}"/>
+    <hyperlink ref="A122" r:id="rId52" xr:uid="{56B02F73-2F13-45B7-976D-964954E8F279}"/>
+    <hyperlink ref="A52" r:id="rId53" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
+    <hyperlink ref="A51" r:id="rId54" xr:uid="{D489065C-0363-4F65-A97E-78D9D1F1CE27}"/>
+    <hyperlink ref="A50" r:id="rId55" xr:uid="{BD93FEB8-E724-420B-A83E-2061ED37CAF2}"/>
+    <hyperlink ref="A191" r:id="rId56" xr:uid="{5D4CB707-D9DF-4336-8079-9A08746A0C3E}"/>
+    <hyperlink ref="A192" r:id="rId57" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
+    <hyperlink ref="A190" r:id="rId58" xr:uid="{96A16812-ED9B-4799-9AFA-DFA51BC408DA}"/>
+    <hyperlink ref="A7" r:id="rId59" xr:uid="{22C5138C-1293-437E-BD1A-D48C932D0D04}"/>
+    <hyperlink ref="A21" r:id="rId60" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
+    <hyperlink ref="A22" r:id="rId61" xr:uid="{5009CD0A-CBCD-41D4-9A4E-8F0A1F817F5C}"/>
+    <hyperlink ref="A23" r:id="rId62" xr:uid="{71D24384-8BF3-443A-B910-7029D965CC2C}"/>
+    <hyperlink ref="A24" r:id="rId63" xr:uid="{A80791BD-384F-4940-BF55-05DE4D7D59D5}"/>
+    <hyperlink ref="A154" r:id="rId64" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A155" r:id="rId65" xr:uid="{18FB7F9C-C3F5-4CA1-8C00-F365ABE9E7B0}"/>
+    <hyperlink ref="A157" r:id="rId66" xr:uid="{16BCB221-1B61-49E4-80D9-7D3BC0B74CD9}"/>
+    <hyperlink ref="A17" r:id="rId67" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A18" r:id="rId68" xr:uid="{7494B6B1-F895-4BD2-966C-FDEEEE6175C6}"/>
+    <hyperlink ref="A19" r:id="rId69" xr:uid="{A7225E7F-C594-4B8B-8385-A0ACE1A92F05}"/>
+    <hyperlink ref="A20" r:id="rId70" xr:uid="{23FE1FF8-50DC-4797-B753-2EE5C1C9B47F}"/>
+    <hyperlink ref="A25" r:id="rId71" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A26" r:id="rId72" xr:uid="{F5BE76AF-7994-4D97-B432-4450F54C3EC3}"/>
+    <hyperlink ref="A27" r:id="rId73" xr:uid="{14702591-FF74-4F77-A775-FC02CDD017BD}"/>
+    <hyperlink ref="A28" r:id="rId74" xr:uid="{E23A852A-F418-4045-8287-B06A43F84279}"/>
+    <hyperlink ref="A173" r:id="rId75" xr:uid="{3FD70B98-7E3D-468D-913D-77ADE4B6D096}"/>
+    <hyperlink ref="A174" r:id="rId76" xr:uid="{14279E30-A53D-4169-A916-9899A72B4335}"/>
+    <hyperlink ref="A175" r:id="rId77" xr:uid="{5B810F6E-1BAC-40EE-9B9B-16BEC438586F}"/>
+    <hyperlink ref="A183" r:id="rId78" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A184" r:id="rId79" xr:uid="{3D67F0ED-B33C-4C7E-B393-51A347B64C72}"/>
+    <hyperlink ref="A176" r:id="rId80" xr:uid="{2D77DE26-68EF-4E17-A593-9E1F611357DF}"/>
+    <hyperlink ref="A178" r:id="rId81" xr:uid="{A425E694-3572-4822-A8BF-CE69E8D101B1}"/>
+    <hyperlink ref="A103" r:id="rId82" xr:uid="{5EF5C1A5-93E3-4292-9E80-3BA88C2778FF}"/>
+    <hyperlink ref="A61" r:id="rId83" xr:uid="{B8FA5090-B2AC-4000-946F-4F8E9F976ABB}"/>
+    <hyperlink ref="A126" r:id="rId84" xr:uid="{33892484-7CC4-4409-83EE-5B8494713305}"/>
+    <hyperlink ref="A116" r:id="rId85" xr:uid="{C8CC2851-6618-4C92-9F7B-F36AF03A62D5}"/>
+    <hyperlink ref="A107" r:id="rId86" xr:uid="{BD9F090B-F993-424A-9D4E-643835A4A1B5}"/>
+    <hyperlink ref="A48" r:id="rId87" xr:uid="{789A0F0B-83F5-44B2-8AF4-E63C03129061}"/>
+    <hyperlink ref="A79" r:id="rId88" xr:uid="{13B06111-51C5-44EB-A417-B423FCF87A9D}"/>
+    <hyperlink ref="A29" r:id="rId89" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{19411F62-23AF-4456-930D-FDDB2525D07E}"/>
+    <hyperlink ref="A30" r:id="rId90" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30C4A7D5-D8D1-44B1-A8F0-6DD08AC706FD}"/>
+    <hyperlink ref="A31" r:id="rId91" xr:uid="{B348F40D-7C16-4EDA-9443-030925167441}"/>
+    <hyperlink ref="A32" r:id="rId92" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1FD6650-FBA0-4A08-8EB3-7ADFBA1EB40B}"/>
+    <hyperlink ref="A56" r:id="rId93" xr:uid="{7239A756-B622-481B-B0CC-88BF1CDE0251}"/>
+    <hyperlink ref="A57" r:id="rId94" xr:uid="{3279BE32-6BDA-4000-B513-6F390C2D801B}"/>
+    <hyperlink ref="A58" r:id="rId95" xr:uid="{B9426E20-0111-489A-ABA5-DE278313D977}"/>
+    <hyperlink ref="A59" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42FBD9F2-2E7F-4B26-83FF-CFF748CA6977}"/>
+    <hyperlink ref="A40" r:id="rId97" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C116B26B-6EA7-47D2-9CB8-4C7E7C37D3D0}"/>
+    <hyperlink ref="A39" r:id="rId98" xr:uid="{CC3B86DF-D0E6-489E-A471-29B23E45F44C}"/>
+    <hyperlink ref="A142" r:id="rId99" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C2E76D46-D38C-4C90-A0B4-6EDF62F894DD}"/>
+    <hyperlink ref="A143" r:id="rId100" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg/960px-A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE7DBEB1-0E52-4957-AEA9-E45AD57C1F2B}"/>
+    <hyperlink ref="A144" r:id="rId101" xr:uid="{F7DF6960-FBA7-4F1F-9318-C93D2A43737E}"/>
+    <hyperlink ref="A95" r:id="rId102" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{352E471E-E731-4E5B-80BA-4999FF5F6B1A}"/>
+    <hyperlink ref="A96" r:id="rId103" xr:uid="{839F1E2A-7006-4DB4-B725-20EF37F9A5C8}"/>
+    <hyperlink ref="A97" r:id="rId104" xr:uid="{500F826C-8278-4BD6-923B-FFE1F8E4354B}"/>
+    <hyperlink ref="A98" r:id="rId105" xr:uid="{B7E0737D-82E1-4F6B-A3C9-6E4EEC6AB3B4}"/>
+    <hyperlink ref="A99" r:id="rId106" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5ADD8BE8-D8E6-4927-A91A-849270396539}"/>
+    <hyperlink ref="A177" r:id="rId107" xr:uid="{93456831-65A0-45D1-A1FF-595F7269BBE8}"/>
+    <hyperlink ref="A46" r:id="rId108" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4555C5B1-E817-46A0-A555-151252E022A5}"/>
+    <hyperlink ref="A81" r:id="rId109" xr:uid="{CB0D0EC8-8997-41A5-91A6-A24DDA0FAC2A}"/>
+    <hyperlink ref="A82" r:id="rId110" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{2439E527-41F8-42E0-B057-02744DA8FE60}"/>
+    <hyperlink ref="A83" r:id="rId111" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A0C89B84-9163-4F09-82BD-E69ED3B1305D}"/>
+    <hyperlink ref="A84" r:id="rId112" xr:uid="{560BFD49-910A-4C7C-9A48-62AA8C707FAE}"/>
+    <hyperlink ref="A185" r:id="rId113" xr:uid="{2D4FDC84-65C6-4B60-8784-01FF2979A025}"/>
+    <hyperlink ref="A156" r:id="rId114" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg/1280px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1316C7CF-63CB-4DE4-9ADA-B275147D6C65}"/>
+    <hyperlink ref="A5" r:id="rId115" xr:uid="{B19C7B9E-5B3D-4724-B6B8-E3C4ACF5C448}"/>
+    <hyperlink ref="A6" r:id="rId116" xr:uid="{2BB3C7BC-AD1B-4130-B24F-A5F7EC731D79}"/>
+    <hyperlink ref="A172" r:id="rId117" xr:uid="{D763752F-FBEC-4CDB-B477-387DC08FC326}"/>
+    <hyperlink ref="A112" r:id="rId118" xr:uid="{227F0108-3A33-4EF7-8CE6-F745BA19BFE4}"/>
+    <hyperlink ref="A111" r:id="rId119" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{884AD666-9BA8-4FF8-8361-4099E5C83320}"/>
+    <hyperlink ref="A118" r:id="rId120" xr:uid="{228C40D6-3E55-48F0-86BE-5BA2F0BCC4BE}"/>
+    <hyperlink ref="A104" r:id="rId121" xr:uid="{F508D20B-0D4F-4533-B30D-2F88B7C973C7}"/>
+    <hyperlink ref="A136" r:id="rId122" xr:uid="{75A7E45B-C227-4CF5-B1E9-D5BDD9B6637C}"/>
+    <hyperlink ref="A3" r:id="rId123" xr:uid="{D44D3FAD-D28B-4520-B8A5-A29F80BFA189}"/>
+    <hyperlink ref="A131" r:id="rId124" xr:uid="{00F1BCF0-13CA-4B43-8DF3-E453747836E7}"/>
+    <hyperlink ref="A44" r:id="rId125" xr:uid="{E0994650-41C9-4C3F-9BEC-FA80935009D9}"/>
+    <hyperlink ref="A43" r:id="rId126" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{253230BE-7E1B-4968-8C55-FA4364F8CBC5}"/>
+    <hyperlink ref="A73" r:id="rId127" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1C944A1-19DC-4371-98A1-A2D838E4F269}"/>
+    <hyperlink ref="A74" r:id="rId128" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg/960px-Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{FA20EED7-AA47-4E03-BE66-AFC50264306C}"/>
+    <hyperlink ref="A94" r:id="rId129" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BE16BF4-DD65-4F27-BBD5-A6EF014B05B6}"/>
+    <hyperlink ref="A93" r:id="rId130" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg/330px-It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE319303-F75E-4837-B1A7-A12164E73405}"/>
+    <hyperlink ref="A92" r:id="rId131" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8FE59364-D9F8-4529-B52B-202CBB40D51C}"/>
+    <hyperlink ref="A91" r:id="rId132" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg/960px-%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{857FA17F-932C-4DF5-8BF0-6FBF572CA2E9}"/>
+    <hyperlink ref="A36" r:id="rId133" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97334409-644B-4C8F-8DD1-C9739DFDCF00}"/>
+    <hyperlink ref="A132" r:id="rId134" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C3E45888-78FB-469F-88EF-4555AC4C5B33}"/>
+    <hyperlink ref="A160" r:id="rId135" xr:uid="{4DAF9F68-C415-4CF3-9F65-589FC5D5CA2B}"/>
+    <hyperlink ref="A171" r:id="rId136" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0906DB65-B8C5-4B3A-8E90-2873AADBC296}"/>
+    <hyperlink ref="A78" r:id="rId137" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg/960px-The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{31AE0316-09BF-4338-B46B-1C75C21E8095}"/>
+    <hyperlink ref="A62" r:id="rId138" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDEE96F0-6E4A-45D0-9AF3-0D0904CC30FA}"/>
+    <hyperlink ref="A64" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg/960px-Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{43E18F07-A342-4B74-B10C-134C04EF4114}"/>
+    <hyperlink ref="A141" r:id="rId140" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DE7EA9C6-77CF-437A-8102-5BD685E8EE51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau3.xlsx
+++ b/quizzes/peinture-18e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CFBC93-0347-464B-8EAE-9354DF528D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4ECC15-0098-46EF-9425-D8AE9965E22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>titre de l’œuvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jean-Antoine Watteau</t>
   </si>
   <si>
@@ -1959,6 +1956,9 @@
   </si>
   <si>
     <t>Élisabeth VIGEE LE BRUN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2469,3402 +2469,3402 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>495</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>405</v>
-      </c>
       <c r="E6" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>407</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>503</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>505</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C20" s="6">
         <v>1775</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C24" s="6">
         <v>1770</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C31" s="9">
         <v>1726</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>585</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>474</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>428</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C37" s="6">
         <v>1789</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>516</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B43" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="E43" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="E44" s="8" t="s">
         <v>381</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>384</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="E46" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>387</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>390</v>
-      </c>
       <c r="D51" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C53" s="6">
         <v>1783</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D55" t="s">
         <v>280</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D55" t="s">
-        <v>281</v>
-      </c>
       <c r="E55" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B56" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>326</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C57" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="E58" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C59" s="9">
         <v>1783</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C61" s="6">
         <v>1750</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="E64" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>485</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>484</v>
-      </c>
       <c r="C66" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B73" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="D73" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="E73" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B74" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>422</v>
-      </c>
       <c r="D74" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C77" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="E78" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B79" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D79" s="8" t="s">
+      <c r="E79" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="E80" s="11" t="s">
         <v>435</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B81" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="D81" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="E81" s="8" t="s">
         <v>353</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E82" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D88" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="E88" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D89" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B91" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="E91" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B92" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D92" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="D92" s="8" t="s">
+      <c r="E92" s="8" t="s">
         <v>448</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B93" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D93" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="E93" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B94" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="E94" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B95" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="D95" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C96" s="9">
         <v>1794</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C97" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D97" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="E97" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C98" s="9">
         <v>1791</v>
       </c>
       <c r="D98" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E98" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C99" s="9">
         <v>1799</v>
       </c>
       <c r="D99" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="5" t="s">
+      <c r="D101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="5" t="s">
+      <c r="D102" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="E102" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="E104" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B105" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="D105" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C106" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C107" s="6">
         <v>1769</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C108" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="C110" s="6">
         <v>1721</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C111" s="9">
         <v>1748</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="C113" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E113" s="5" t="s">
         <v>490</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D114" s="5" t="s">
+      <c r="E114" s="5" t="s">
         <v>493</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="D115" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" s="6">
         <v>1771</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="D117" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E117" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C118" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D118" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D118" s="8" t="s">
+      <c r="E118" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B119" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C119" s="5" t="s">
+      <c r="D119" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="C120" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="D120" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E120" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D121" t="s">
         <v>371</v>
       </c>
-      <c r="B121" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="E121" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E122" s="5" t="s">
         <v>374</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="D123" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="E123" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B124" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C124" s="5" t="s">
+      <c r="D124" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C125" s="5" t="s">
+      <c r="D125" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C126" s="6">
         <v>1769</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B127" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C127" s="5" t="s">
+      <c r="D127" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="E127" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B132" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="D132" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="E132" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C133" s="5" t="s">
+      <c r="D133" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C134" s="5" t="s">
+      <c r="D134" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E134" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C135" s="5" t="s">
+      <c r="D135" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="E135" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="C139" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="D139" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E140" s="5" t="s">
         <v>522</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D141" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="E141" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B142" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E142" s="8" t="s">
         <v>509</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D143" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E143" s="8" t="s">
         <v>511</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C144" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E144" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="C145" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="D145" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="E145" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B146" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C146" s="5" t="s">
+      <c r="D146" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D147" s="5" t="s">
+      <c r="E147" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C148" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="D149" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="E149" s="5" t="s">
         <v>542</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E150" s="5" t="s">
         <v>544</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D151" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="B151" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D151" s="5" t="s">
+      <c r="E151" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="C152" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="C152" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D152" s="5" t="s">
+      <c r="E152" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="E153" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="C154" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E154" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C156" s="9">
         <v>1772</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E157" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="D158" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D159" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B159" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D159" s="5" t="s">
+      <c r="E159" s="5" t="s">
         <v>530</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D160" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="E160" s="8" t="s">
         <v>532</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C161" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="B161" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C161" s="5" t="s">
+      <c r="D161" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>535</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>460</v>
       </c>
       <c r="C166" s="6">
         <v>1760</v>
       </c>
       <c r="D166" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E166" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="B167" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C167" s="5" t="s">
+      <c r="D167" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="E167" s="5" t="s">
         <v>551</v>
-      </c>
-      <c r="E167" s="5" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D168" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="B168" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D168" s="5" t="s">
+      <c r="E168" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="C169" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="D169" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="5" t="s">
         <v>465</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C170" s="6">
         <v>1710</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C171" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E171" s="8" t="s">
         <v>469</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B172" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D172" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C172" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D172" s="8" t="s">
+      <c r="E172" s="8" t="s">
         <v>283</v>
-      </c>
-      <c r="E172" s="8" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B173" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C173" s="5" t="s">
+      <c r="D173" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D173" s="5" t="s">
+      <c r="E173" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="C176" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D176" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C176" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D176" s="5" t="s">
+      <c r="E176" s="5" t="s">
         <v>306</v>
-      </c>
-      <c r="E176" s="5" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C177" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D177" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="D177" s="8" t="s">
+      <c r="E177" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="C183" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="D183" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D183" s="5" t="s">
+      <c r="E183" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C184" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B184" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C184" s="5" t="s">
+      <c r="D184" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="E184" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C185" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="D185" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="C186" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="D186" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E186" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C187" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B187" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C187" s="5" t="s">
+      <c r="D187" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D187" s="5" t="s">
+      <c r="E187" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C188" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B188" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C188" s="5" t="s">
+      <c r="D188" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E188" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E189" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B190" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="C190" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="C190" s="5" t="s">
+      <c r="D190" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="B191" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C191" s="5" t="s">
+      <c r="D191" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E191" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C192" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B192" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C192" s="5" t="s">
+      <c r="D192" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E192" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B193" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="C193" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C193" s="5" t="s">
+      <c r="D193" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E193" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C194" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B194" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C194" s="5" t="s">
+      <c r="D194" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E194" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C195" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B195" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C195" s="5" t="s">
+      <c r="D195" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D195" s="5" t="s">
+      <c r="E195" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E196" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D196" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="E198" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="E199" s="5" t="s">
         <v>570</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="E199" s="5" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E200" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D200" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="E200" s="5" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B201" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -5872,146 +5872,146 @@
     <sortCondition ref="B2:B201"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A100" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A101" r:id="rId2" xr:uid="{01BEB8B3-FA8A-46D2-A3F2-A16DDC5DC041}"/>
-    <hyperlink ref="A102" r:id="rId3" xr:uid="{632107C4-0CA6-4716-AF0C-9917625D9347}"/>
-    <hyperlink ref="A60" r:id="rId4" xr:uid="{546B8D2D-6935-4CFE-A108-C653923A76FA}"/>
-    <hyperlink ref="A63" r:id="rId5" xr:uid="{EA46CCD8-B590-4A96-8E08-7366BE83116E}"/>
-    <hyperlink ref="A123" r:id="rId6" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A124" r:id="rId7" xr:uid="{35E3E0C5-7760-4EB4-A63D-8DC2B45AB000}"/>
-    <hyperlink ref="A125" r:id="rId8" xr:uid="{AA3677AF-F09C-418C-BA66-01C1E134A694}"/>
-    <hyperlink ref="A127" r:id="rId9" xr:uid="{EE8CD801-4C81-44EB-A625-9BD03F98AE32}"/>
-    <hyperlink ref="A115" r:id="rId10" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A117" r:id="rId11" xr:uid="{E16F0F03-CFFD-42C7-A057-4946BCDB4EC0}"/>
-    <hyperlink ref="A119" r:id="rId12" xr:uid="{251BF111-7C01-4C51-B32A-BDBEEDC7FE67}"/>
-    <hyperlink ref="A146" r:id="rId13" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A106" r:id="rId14" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A164" r:id="rId15" xr:uid="{35843622-C449-41E5-858B-122E86FE5585}"/>
-    <hyperlink ref="A41" r:id="rId16" xr:uid="{576FD0EA-8E95-4DD9-9DE2-D6D386132173}"/>
-    <hyperlink ref="A108" r:id="rId17" xr:uid="{FECCE726-C931-490B-A82B-00D49DAE2D1A}"/>
-    <hyperlink ref="A148" r:id="rId18" xr:uid="{B4CACE6B-4585-40BF-9570-7E775FC2373D}"/>
-    <hyperlink ref="A105" r:id="rId19" xr:uid="{8A76ADFE-8287-4A33-8D3C-7E7D0281B24E}"/>
-    <hyperlink ref="A70" r:id="rId20" xr:uid="{69DF61A4-652A-4BEC-9D5E-20122E52140C}"/>
-    <hyperlink ref="A54" r:id="rId21" xr:uid="{A706DABA-E5F6-4965-92B2-0B4D8EECE9A9}"/>
-    <hyperlink ref="A53" r:id="rId22" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A55" r:id="rId23" xr:uid="{28DCFBA1-50BA-44D0-B4C1-3DCB2A899994}"/>
-    <hyperlink ref="A140" r:id="rId24" xr:uid="{6FEB838B-F605-42FF-BEC0-808745C25F46}"/>
-    <hyperlink ref="A139" r:id="rId25" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
-    <hyperlink ref="A42" r:id="rId26" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
-    <hyperlink ref="A10" r:id="rId27" xr:uid="{6052EA8F-A06C-4030-B911-93D5F34BB1AB}"/>
-    <hyperlink ref="A9" r:id="rId28" xr:uid="{5050CD76-E020-42D7-8372-6A028F57267B}"/>
-    <hyperlink ref="A8" r:id="rId29" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
-    <hyperlink ref="A4" r:id="rId30" xr:uid="{2D892170-F3ED-462C-A0E6-BF99CECAEBAD}"/>
-    <hyperlink ref="A2" r:id="rId31" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A113" r:id="rId32" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A114" r:id="rId33" xr:uid="{ADA8E203-9BC6-4247-8126-40DD148927E8}"/>
-    <hyperlink ref="A66" r:id="rId34" xr:uid="{244B0B97-E64F-48EE-8997-BE484716E578}"/>
-    <hyperlink ref="A65" r:id="rId35" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
-    <hyperlink ref="A169" r:id="rId36" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A170" r:id="rId37" xr:uid="{C00F019D-685D-4B14-981E-47081DD2F058}"/>
-    <hyperlink ref="A33" r:id="rId38" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A34" r:id="rId39" xr:uid="{F9DC5954-BBFC-4D2C-A9D5-F511742D050E}"/>
-    <hyperlink ref="A35" r:id="rId40" xr:uid="{F271E2E7-24F4-4198-BC26-73393C3369D5}"/>
-    <hyperlink ref="A110" r:id="rId41" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A166" r:id="rId42" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
-    <hyperlink ref="A152" r:id="rId43" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
-    <hyperlink ref="A153" r:id="rId44" xr:uid="{E768E684-8D4F-4A90-9C29-53B564F3AEEE}"/>
-    <hyperlink ref="A37" r:id="rId45" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
-    <hyperlink ref="A80" r:id="rId46" xr:uid="{A4967510-4B31-45B5-A9EF-9DF2BC4D2F52}"/>
-    <hyperlink ref="A45" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/e/e8/Dmitry_Levitsky_-_%D0%9F%D0%BE%D1%80%D1%82%D1%80%D0%B5%D1%82_%D0%9C.%D0%90.%D0%94%D1%8C%D1%8F%D0%BA%D0%BE%D0%B2%D0%BE%D0%B9_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{423F91D2-34B4-4D68-AE3C-F51AE35E6DBD}"/>
-    <hyperlink ref="A15" r:id="rId48" xr:uid="{8617592A-0D68-45CD-9E0E-E1DF6D1ED620}"/>
-    <hyperlink ref="A16" r:id="rId49" xr:uid="{FCB01430-72BF-469A-9077-75F553B76135}"/>
-    <hyperlink ref="A120" r:id="rId50" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
-    <hyperlink ref="A121" r:id="rId51" xr:uid="{498C856B-1FBB-43D0-AC72-2E0AF7437ADF}"/>
-    <hyperlink ref="A122" r:id="rId52" xr:uid="{56B02F73-2F13-45B7-976D-964954E8F279}"/>
-    <hyperlink ref="A52" r:id="rId53" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
-    <hyperlink ref="A51" r:id="rId54" xr:uid="{D489065C-0363-4F65-A97E-78D9D1F1CE27}"/>
-    <hyperlink ref="A50" r:id="rId55" xr:uid="{BD93FEB8-E724-420B-A83E-2061ED37CAF2}"/>
-    <hyperlink ref="A191" r:id="rId56" xr:uid="{5D4CB707-D9DF-4336-8079-9A08746A0C3E}"/>
-    <hyperlink ref="A192" r:id="rId57" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
-    <hyperlink ref="A190" r:id="rId58" xr:uid="{96A16812-ED9B-4799-9AFA-DFA51BC408DA}"/>
-    <hyperlink ref="A7" r:id="rId59" xr:uid="{22C5138C-1293-437E-BD1A-D48C932D0D04}"/>
-    <hyperlink ref="A21" r:id="rId60" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
-    <hyperlink ref="A22" r:id="rId61" xr:uid="{5009CD0A-CBCD-41D4-9A4E-8F0A1F817F5C}"/>
-    <hyperlink ref="A23" r:id="rId62" xr:uid="{71D24384-8BF3-443A-B910-7029D965CC2C}"/>
-    <hyperlink ref="A24" r:id="rId63" xr:uid="{A80791BD-384F-4940-BF55-05DE4D7D59D5}"/>
-    <hyperlink ref="A154" r:id="rId64" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A155" r:id="rId65" xr:uid="{18FB7F9C-C3F5-4CA1-8C00-F365ABE9E7B0}"/>
-    <hyperlink ref="A157" r:id="rId66" xr:uid="{16BCB221-1B61-49E4-80D9-7D3BC0B74CD9}"/>
-    <hyperlink ref="A17" r:id="rId67" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A18" r:id="rId68" xr:uid="{7494B6B1-F895-4BD2-966C-FDEEEE6175C6}"/>
-    <hyperlink ref="A19" r:id="rId69" xr:uid="{A7225E7F-C594-4B8B-8385-A0ACE1A92F05}"/>
-    <hyperlink ref="A20" r:id="rId70" xr:uid="{23FE1FF8-50DC-4797-B753-2EE5C1C9B47F}"/>
-    <hyperlink ref="A25" r:id="rId71" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A26" r:id="rId72" xr:uid="{F5BE76AF-7994-4D97-B432-4450F54C3EC3}"/>
-    <hyperlink ref="A27" r:id="rId73" xr:uid="{14702591-FF74-4F77-A775-FC02CDD017BD}"/>
-    <hyperlink ref="A28" r:id="rId74" xr:uid="{E23A852A-F418-4045-8287-B06A43F84279}"/>
-    <hyperlink ref="A173" r:id="rId75" xr:uid="{3FD70B98-7E3D-468D-913D-77ADE4B6D096}"/>
-    <hyperlink ref="A174" r:id="rId76" xr:uid="{14279E30-A53D-4169-A916-9899A72B4335}"/>
-    <hyperlink ref="A175" r:id="rId77" xr:uid="{5B810F6E-1BAC-40EE-9B9B-16BEC438586F}"/>
-    <hyperlink ref="A183" r:id="rId78" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A184" r:id="rId79" xr:uid="{3D67F0ED-B33C-4C7E-B393-51A347B64C72}"/>
-    <hyperlink ref="A176" r:id="rId80" xr:uid="{2D77DE26-68EF-4E17-A593-9E1F611357DF}"/>
-    <hyperlink ref="A178" r:id="rId81" xr:uid="{A425E694-3572-4822-A8BF-CE69E8D101B1}"/>
-    <hyperlink ref="A103" r:id="rId82" xr:uid="{5EF5C1A5-93E3-4292-9E80-3BA88C2778FF}"/>
-    <hyperlink ref="A61" r:id="rId83" xr:uid="{B8FA5090-B2AC-4000-946F-4F8E9F976ABB}"/>
-    <hyperlink ref="A126" r:id="rId84" xr:uid="{33892484-7CC4-4409-83EE-5B8494713305}"/>
-    <hyperlink ref="A116" r:id="rId85" xr:uid="{C8CC2851-6618-4C92-9F7B-F36AF03A62D5}"/>
-    <hyperlink ref="A107" r:id="rId86" xr:uid="{BD9F090B-F993-424A-9D4E-643835A4A1B5}"/>
-    <hyperlink ref="A48" r:id="rId87" xr:uid="{789A0F0B-83F5-44B2-8AF4-E63C03129061}"/>
-    <hyperlink ref="A79" r:id="rId88" xr:uid="{13B06111-51C5-44EB-A417-B423FCF87A9D}"/>
-    <hyperlink ref="A29" r:id="rId89" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{19411F62-23AF-4456-930D-FDDB2525D07E}"/>
-    <hyperlink ref="A30" r:id="rId90" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30C4A7D5-D8D1-44B1-A8F0-6DD08AC706FD}"/>
-    <hyperlink ref="A31" r:id="rId91" xr:uid="{B348F40D-7C16-4EDA-9443-030925167441}"/>
-    <hyperlink ref="A32" r:id="rId92" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1FD6650-FBA0-4A08-8EB3-7ADFBA1EB40B}"/>
-    <hyperlink ref="A56" r:id="rId93" xr:uid="{7239A756-B622-481B-B0CC-88BF1CDE0251}"/>
-    <hyperlink ref="A57" r:id="rId94" xr:uid="{3279BE32-6BDA-4000-B513-6F390C2D801B}"/>
-    <hyperlink ref="A58" r:id="rId95" xr:uid="{B9426E20-0111-489A-ABA5-DE278313D977}"/>
-    <hyperlink ref="A59" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42FBD9F2-2E7F-4B26-83FF-CFF748CA6977}"/>
-    <hyperlink ref="A40" r:id="rId97" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C116B26B-6EA7-47D2-9CB8-4C7E7C37D3D0}"/>
-    <hyperlink ref="A39" r:id="rId98" xr:uid="{CC3B86DF-D0E6-489E-A471-29B23E45F44C}"/>
-    <hyperlink ref="A142" r:id="rId99" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C2E76D46-D38C-4C90-A0B4-6EDF62F894DD}"/>
-    <hyperlink ref="A143" r:id="rId100" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg/960px-A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE7DBEB1-0E52-4957-AEA9-E45AD57C1F2B}"/>
-    <hyperlink ref="A144" r:id="rId101" xr:uid="{F7DF6960-FBA7-4F1F-9318-C93D2A43737E}"/>
-    <hyperlink ref="A95" r:id="rId102" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{352E471E-E731-4E5B-80BA-4999FF5F6B1A}"/>
-    <hyperlink ref="A96" r:id="rId103" xr:uid="{839F1E2A-7006-4DB4-B725-20EF37F9A5C8}"/>
-    <hyperlink ref="A97" r:id="rId104" xr:uid="{500F826C-8278-4BD6-923B-FFE1F8E4354B}"/>
-    <hyperlink ref="A98" r:id="rId105" xr:uid="{B7E0737D-82E1-4F6B-A3C9-6E4EEC6AB3B4}"/>
-    <hyperlink ref="A99" r:id="rId106" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5ADD8BE8-D8E6-4927-A91A-849270396539}"/>
-    <hyperlink ref="A177" r:id="rId107" xr:uid="{93456831-65A0-45D1-A1FF-595F7269BBE8}"/>
-    <hyperlink ref="A46" r:id="rId108" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4555C5B1-E817-46A0-A555-151252E022A5}"/>
-    <hyperlink ref="A81" r:id="rId109" xr:uid="{CB0D0EC8-8997-41A5-91A6-A24DDA0FAC2A}"/>
-    <hyperlink ref="A82" r:id="rId110" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{2439E527-41F8-42E0-B057-02744DA8FE60}"/>
-    <hyperlink ref="A83" r:id="rId111" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A0C89B84-9163-4F09-82BD-E69ED3B1305D}"/>
-    <hyperlink ref="A84" r:id="rId112" xr:uid="{560BFD49-910A-4C7C-9A48-62AA8C707FAE}"/>
-    <hyperlink ref="A185" r:id="rId113" xr:uid="{2D4FDC84-65C6-4B60-8784-01FF2979A025}"/>
-    <hyperlink ref="A156" r:id="rId114" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg/1280px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1316C7CF-63CB-4DE4-9ADA-B275147D6C65}"/>
-    <hyperlink ref="A5" r:id="rId115" xr:uid="{B19C7B9E-5B3D-4724-B6B8-E3C4ACF5C448}"/>
-    <hyperlink ref="A6" r:id="rId116" xr:uid="{2BB3C7BC-AD1B-4130-B24F-A5F7EC731D79}"/>
-    <hyperlink ref="A172" r:id="rId117" xr:uid="{D763752F-FBEC-4CDB-B477-387DC08FC326}"/>
-    <hyperlink ref="A112" r:id="rId118" xr:uid="{227F0108-3A33-4EF7-8CE6-F745BA19BFE4}"/>
-    <hyperlink ref="A111" r:id="rId119" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{884AD666-9BA8-4FF8-8361-4099E5C83320}"/>
-    <hyperlink ref="A118" r:id="rId120" xr:uid="{228C40D6-3E55-48F0-86BE-5BA2F0BCC4BE}"/>
-    <hyperlink ref="A104" r:id="rId121" xr:uid="{F508D20B-0D4F-4533-B30D-2F88B7C973C7}"/>
-    <hyperlink ref="A136" r:id="rId122" xr:uid="{75A7E45B-C227-4CF5-B1E9-D5BDD9B6637C}"/>
-    <hyperlink ref="A3" r:id="rId123" xr:uid="{D44D3FAD-D28B-4520-B8A5-A29F80BFA189}"/>
-    <hyperlink ref="A131" r:id="rId124" xr:uid="{00F1BCF0-13CA-4B43-8DF3-E453747836E7}"/>
-    <hyperlink ref="A44" r:id="rId125" xr:uid="{E0994650-41C9-4C3F-9BEC-FA80935009D9}"/>
-    <hyperlink ref="A43" r:id="rId126" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{253230BE-7E1B-4968-8C55-FA4364F8CBC5}"/>
-    <hyperlink ref="A73" r:id="rId127" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1C944A1-19DC-4371-98A1-A2D838E4F269}"/>
-    <hyperlink ref="A74" r:id="rId128" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg/960px-Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{FA20EED7-AA47-4E03-BE66-AFC50264306C}"/>
-    <hyperlink ref="A94" r:id="rId129" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BE16BF4-DD65-4F27-BBD5-A6EF014B05B6}"/>
-    <hyperlink ref="A93" r:id="rId130" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg/330px-It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE319303-F75E-4837-B1A7-A12164E73405}"/>
-    <hyperlink ref="A92" r:id="rId131" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8FE59364-D9F8-4529-B52B-202CBB40D51C}"/>
-    <hyperlink ref="A91" r:id="rId132" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg/960px-%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{857FA17F-932C-4DF5-8BF0-6FBF572CA2E9}"/>
-    <hyperlink ref="A36" r:id="rId133" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97334409-644B-4C8F-8DD1-C9739DFDCF00}"/>
-    <hyperlink ref="A132" r:id="rId134" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C3E45888-78FB-469F-88EF-4555AC4C5B33}"/>
-    <hyperlink ref="A160" r:id="rId135" xr:uid="{4DAF9F68-C415-4CF3-9F65-589FC5D5CA2B}"/>
-    <hyperlink ref="A171" r:id="rId136" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0906DB65-B8C5-4B3A-8E90-2873AADBC296}"/>
-    <hyperlink ref="A78" r:id="rId137" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg/960px-The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{31AE0316-09BF-4338-B46B-1C75C21E8095}"/>
-    <hyperlink ref="A62" r:id="rId138" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDEE96F0-6E4A-45D0-9AF3-0D0904CC30FA}"/>
-    <hyperlink ref="A64" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg/960px-Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{43E18F07-A342-4B74-B10C-134C04EF4114}"/>
-    <hyperlink ref="A141" r:id="rId140" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DE7EA9C6-77CF-437A-8102-5BD685E8EE51}"/>
+    <hyperlink ref="A101" r:id="rId1" xr:uid="{01BEB8B3-FA8A-46D2-A3F2-A16DDC5DC041}"/>
+    <hyperlink ref="A102" r:id="rId2" xr:uid="{632107C4-0CA6-4716-AF0C-9917625D9347}"/>
+    <hyperlink ref="A60" r:id="rId3" xr:uid="{546B8D2D-6935-4CFE-A108-C653923A76FA}"/>
+    <hyperlink ref="A63" r:id="rId4" xr:uid="{EA46CCD8-B590-4A96-8E08-7366BE83116E}"/>
+    <hyperlink ref="A123" r:id="rId5" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A124" r:id="rId6" xr:uid="{35E3E0C5-7760-4EB4-A63D-8DC2B45AB000}"/>
+    <hyperlink ref="A125" r:id="rId7" xr:uid="{AA3677AF-F09C-418C-BA66-01C1E134A694}"/>
+    <hyperlink ref="A127" r:id="rId8" xr:uid="{EE8CD801-4C81-44EB-A625-9BD03F98AE32}"/>
+    <hyperlink ref="A115" r:id="rId9" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A117" r:id="rId10" xr:uid="{E16F0F03-CFFD-42C7-A057-4946BCDB4EC0}"/>
+    <hyperlink ref="A119" r:id="rId11" xr:uid="{251BF111-7C01-4C51-B32A-BDBEEDC7FE67}"/>
+    <hyperlink ref="A146" r:id="rId12" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A106" r:id="rId13" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A164" r:id="rId14" xr:uid="{35843622-C449-41E5-858B-122E86FE5585}"/>
+    <hyperlink ref="A41" r:id="rId15" xr:uid="{576FD0EA-8E95-4DD9-9DE2-D6D386132173}"/>
+    <hyperlink ref="A108" r:id="rId16" xr:uid="{FECCE726-C931-490B-A82B-00D49DAE2D1A}"/>
+    <hyperlink ref="A148" r:id="rId17" xr:uid="{B4CACE6B-4585-40BF-9570-7E775FC2373D}"/>
+    <hyperlink ref="A105" r:id="rId18" xr:uid="{8A76ADFE-8287-4A33-8D3C-7E7D0281B24E}"/>
+    <hyperlink ref="A70" r:id="rId19" xr:uid="{69DF61A4-652A-4BEC-9D5E-20122E52140C}"/>
+    <hyperlink ref="A54" r:id="rId20" xr:uid="{A706DABA-E5F6-4965-92B2-0B4D8EECE9A9}"/>
+    <hyperlink ref="A53" r:id="rId21" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A55" r:id="rId22" xr:uid="{28DCFBA1-50BA-44D0-B4C1-3DCB2A899994}"/>
+    <hyperlink ref="A140" r:id="rId23" xr:uid="{6FEB838B-F605-42FF-BEC0-808745C25F46}"/>
+    <hyperlink ref="A139" r:id="rId24" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
+    <hyperlink ref="A42" r:id="rId25" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
+    <hyperlink ref="A10" r:id="rId26" xr:uid="{6052EA8F-A06C-4030-B911-93D5F34BB1AB}"/>
+    <hyperlink ref="A9" r:id="rId27" xr:uid="{5050CD76-E020-42D7-8372-6A028F57267B}"/>
+    <hyperlink ref="A8" r:id="rId28" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
+    <hyperlink ref="A4" r:id="rId29" xr:uid="{2D892170-F3ED-462C-A0E6-BF99CECAEBAD}"/>
+    <hyperlink ref="A2" r:id="rId30" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A113" r:id="rId31" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A114" r:id="rId32" xr:uid="{ADA8E203-9BC6-4247-8126-40DD148927E8}"/>
+    <hyperlink ref="A66" r:id="rId33" xr:uid="{244B0B97-E64F-48EE-8997-BE484716E578}"/>
+    <hyperlink ref="A65" r:id="rId34" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
+    <hyperlink ref="A169" r:id="rId35" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A170" r:id="rId36" xr:uid="{C00F019D-685D-4B14-981E-47081DD2F058}"/>
+    <hyperlink ref="A33" r:id="rId37" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A34" r:id="rId38" xr:uid="{F9DC5954-BBFC-4D2C-A9D5-F511742D050E}"/>
+    <hyperlink ref="A35" r:id="rId39" xr:uid="{F271E2E7-24F4-4198-BC26-73393C3369D5}"/>
+    <hyperlink ref="A110" r:id="rId40" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A166" r:id="rId41" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
+    <hyperlink ref="A152" r:id="rId42" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
+    <hyperlink ref="A153" r:id="rId43" xr:uid="{E768E684-8D4F-4A90-9C29-53B564F3AEEE}"/>
+    <hyperlink ref="A37" r:id="rId44" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
+    <hyperlink ref="A80" r:id="rId45" xr:uid="{A4967510-4B31-45B5-A9EF-9DF2BC4D2F52}"/>
+    <hyperlink ref="A45" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/e/e8/Dmitry_Levitsky_-_%D0%9F%D0%BE%D1%80%D1%82%D1%80%D0%B5%D1%82_%D0%9C.%D0%90.%D0%94%D1%8C%D1%8F%D0%BA%D0%BE%D0%B2%D0%BE%D0%B9_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{423F91D2-34B4-4D68-AE3C-F51AE35E6DBD}"/>
+    <hyperlink ref="A15" r:id="rId47" xr:uid="{8617592A-0D68-45CD-9E0E-E1DF6D1ED620}"/>
+    <hyperlink ref="A16" r:id="rId48" xr:uid="{FCB01430-72BF-469A-9077-75F553B76135}"/>
+    <hyperlink ref="A120" r:id="rId49" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
+    <hyperlink ref="A121" r:id="rId50" xr:uid="{498C856B-1FBB-43D0-AC72-2E0AF7437ADF}"/>
+    <hyperlink ref="A122" r:id="rId51" xr:uid="{56B02F73-2F13-45B7-976D-964954E8F279}"/>
+    <hyperlink ref="A52" r:id="rId52" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
+    <hyperlink ref="A51" r:id="rId53" xr:uid="{D489065C-0363-4F65-A97E-78D9D1F1CE27}"/>
+    <hyperlink ref="A50" r:id="rId54" xr:uid="{BD93FEB8-E724-420B-A83E-2061ED37CAF2}"/>
+    <hyperlink ref="A191" r:id="rId55" xr:uid="{5D4CB707-D9DF-4336-8079-9A08746A0C3E}"/>
+    <hyperlink ref="A192" r:id="rId56" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
+    <hyperlink ref="A190" r:id="rId57" xr:uid="{96A16812-ED9B-4799-9AFA-DFA51BC408DA}"/>
+    <hyperlink ref="A7" r:id="rId58" xr:uid="{22C5138C-1293-437E-BD1A-D48C932D0D04}"/>
+    <hyperlink ref="A21" r:id="rId59" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
+    <hyperlink ref="A22" r:id="rId60" xr:uid="{5009CD0A-CBCD-41D4-9A4E-8F0A1F817F5C}"/>
+    <hyperlink ref="A23" r:id="rId61" xr:uid="{71D24384-8BF3-443A-B910-7029D965CC2C}"/>
+    <hyperlink ref="A24" r:id="rId62" xr:uid="{A80791BD-384F-4940-BF55-05DE4D7D59D5}"/>
+    <hyperlink ref="A154" r:id="rId63" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A155" r:id="rId64" xr:uid="{18FB7F9C-C3F5-4CA1-8C00-F365ABE9E7B0}"/>
+    <hyperlink ref="A157" r:id="rId65" xr:uid="{16BCB221-1B61-49E4-80D9-7D3BC0B74CD9}"/>
+    <hyperlink ref="A17" r:id="rId66" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A18" r:id="rId67" xr:uid="{7494B6B1-F895-4BD2-966C-FDEEEE6175C6}"/>
+    <hyperlink ref="A19" r:id="rId68" xr:uid="{A7225E7F-C594-4B8B-8385-A0ACE1A92F05}"/>
+    <hyperlink ref="A20" r:id="rId69" xr:uid="{23FE1FF8-50DC-4797-B753-2EE5C1C9B47F}"/>
+    <hyperlink ref="A25" r:id="rId70" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A26" r:id="rId71" xr:uid="{F5BE76AF-7994-4D97-B432-4450F54C3EC3}"/>
+    <hyperlink ref="A27" r:id="rId72" xr:uid="{14702591-FF74-4F77-A775-FC02CDD017BD}"/>
+    <hyperlink ref="A28" r:id="rId73" xr:uid="{E23A852A-F418-4045-8287-B06A43F84279}"/>
+    <hyperlink ref="A173" r:id="rId74" xr:uid="{3FD70B98-7E3D-468D-913D-77ADE4B6D096}"/>
+    <hyperlink ref="A174" r:id="rId75" xr:uid="{14279E30-A53D-4169-A916-9899A72B4335}"/>
+    <hyperlink ref="A175" r:id="rId76" xr:uid="{5B810F6E-1BAC-40EE-9B9B-16BEC438586F}"/>
+    <hyperlink ref="A183" r:id="rId77" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A184" r:id="rId78" xr:uid="{3D67F0ED-B33C-4C7E-B393-51A347B64C72}"/>
+    <hyperlink ref="A176" r:id="rId79" xr:uid="{2D77DE26-68EF-4E17-A593-9E1F611357DF}"/>
+    <hyperlink ref="A178" r:id="rId80" xr:uid="{A425E694-3572-4822-A8BF-CE69E8D101B1}"/>
+    <hyperlink ref="A103" r:id="rId81" xr:uid="{5EF5C1A5-93E3-4292-9E80-3BA88C2778FF}"/>
+    <hyperlink ref="A61" r:id="rId82" xr:uid="{B8FA5090-B2AC-4000-946F-4F8E9F976ABB}"/>
+    <hyperlink ref="A126" r:id="rId83" xr:uid="{33892484-7CC4-4409-83EE-5B8494713305}"/>
+    <hyperlink ref="A116" r:id="rId84" xr:uid="{C8CC2851-6618-4C92-9F7B-F36AF03A62D5}"/>
+    <hyperlink ref="A107" r:id="rId85" xr:uid="{BD9F090B-F993-424A-9D4E-643835A4A1B5}"/>
+    <hyperlink ref="A48" r:id="rId86" xr:uid="{789A0F0B-83F5-44B2-8AF4-E63C03129061}"/>
+    <hyperlink ref="A79" r:id="rId87" xr:uid="{13B06111-51C5-44EB-A417-B423FCF87A9D}"/>
+    <hyperlink ref="A29" r:id="rId88" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{19411F62-23AF-4456-930D-FDDB2525D07E}"/>
+    <hyperlink ref="A30" r:id="rId89" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30C4A7D5-D8D1-44B1-A8F0-6DD08AC706FD}"/>
+    <hyperlink ref="A31" r:id="rId90" xr:uid="{B348F40D-7C16-4EDA-9443-030925167441}"/>
+    <hyperlink ref="A32" r:id="rId91" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1FD6650-FBA0-4A08-8EB3-7ADFBA1EB40B}"/>
+    <hyperlink ref="A56" r:id="rId92" xr:uid="{7239A756-B622-481B-B0CC-88BF1CDE0251}"/>
+    <hyperlink ref="A57" r:id="rId93" xr:uid="{3279BE32-6BDA-4000-B513-6F390C2D801B}"/>
+    <hyperlink ref="A58" r:id="rId94" xr:uid="{B9426E20-0111-489A-ABA5-DE278313D977}"/>
+    <hyperlink ref="A59" r:id="rId95" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42FBD9F2-2E7F-4B26-83FF-CFF748CA6977}"/>
+    <hyperlink ref="A40" r:id="rId96" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C116B26B-6EA7-47D2-9CB8-4C7E7C37D3D0}"/>
+    <hyperlink ref="A39" r:id="rId97" xr:uid="{CC3B86DF-D0E6-489E-A471-29B23E45F44C}"/>
+    <hyperlink ref="A142" r:id="rId98" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C2E76D46-D38C-4C90-A0B4-6EDF62F894DD}"/>
+    <hyperlink ref="A143" r:id="rId99" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg/960px-A_Blacksmith%27s_Shop_1771_Joseph_Wright_of_Derby_-_54977535752.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE7DBEB1-0E52-4957-AEA9-E45AD57C1F2B}"/>
+    <hyperlink ref="A144" r:id="rId100" xr:uid="{F7DF6960-FBA7-4F1F-9318-C93D2A43737E}"/>
+    <hyperlink ref="A95" r:id="rId101" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{352E471E-E731-4E5B-80BA-4999FF5F6B1A}"/>
+    <hyperlink ref="A96" r:id="rId102" xr:uid="{839F1E2A-7006-4DB4-B725-20EF37F9A5C8}"/>
+    <hyperlink ref="A97" r:id="rId103" xr:uid="{500F826C-8278-4BD6-923B-FFE1F8E4354B}"/>
+    <hyperlink ref="A98" r:id="rId104" xr:uid="{B7E0737D-82E1-4F6B-A3C9-6E4EEC6AB3B4}"/>
+    <hyperlink ref="A99" r:id="rId105" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5ADD8BE8-D8E6-4927-A91A-849270396539}"/>
+    <hyperlink ref="A177" r:id="rId106" xr:uid="{93456831-65A0-45D1-A1FF-595F7269BBE8}"/>
+    <hyperlink ref="A46" r:id="rId107" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4555C5B1-E817-46A0-A555-151252E022A5}"/>
+    <hyperlink ref="A81" r:id="rId108" xr:uid="{CB0D0EC8-8997-41A5-91A6-A24DDA0FAC2A}"/>
+    <hyperlink ref="A82" r:id="rId109" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{2439E527-41F8-42E0-B057-02744DA8FE60}"/>
+    <hyperlink ref="A83" r:id="rId110" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A0C89B84-9163-4F09-82BD-E69ED3B1305D}"/>
+    <hyperlink ref="A84" r:id="rId111" xr:uid="{560BFD49-910A-4C7C-9A48-62AA8C707FAE}"/>
+    <hyperlink ref="A185" r:id="rId112" xr:uid="{2D4FDC84-65C6-4B60-8784-01FF2979A025}"/>
+    <hyperlink ref="A156" r:id="rId113" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg/1280px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Melon_and_Pears_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1316C7CF-63CB-4DE4-9ADA-B275147D6C65}"/>
+    <hyperlink ref="A5" r:id="rId114" xr:uid="{B19C7B9E-5B3D-4724-B6B8-E3C4ACF5C448}"/>
+    <hyperlink ref="A6" r:id="rId115" xr:uid="{2BB3C7BC-AD1B-4130-B24F-A5F7EC731D79}"/>
+    <hyperlink ref="A172" r:id="rId116" xr:uid="{D763752F-FBEC-4CDB-B477-387DC08FC326}"/>
+    <hyperlink ref="A112" r:id="rId117" xr:uid="{227F0108-3A33-4EF7-8CE6-F745BA19BFE4}"/>
+    <hyperlink ref="A111" r:id="rId118" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{884AD666-9BA8-4FF8-8361-4099E5C83320}"/>
+    <hyperlink ref="A118" r:id="rId119" xr:uid="{228C40D6-3E55-48F0-86BE-5BA2F0BCC4BE}"/>
+    <hyperlink ref="A104" r:id="rId120" xr:uid="{F508D20B-0D4F-4533-B30D-2F88B7C973C7}"/>
+    <hyperlink ref="A136" r:id="rId121" xr:uid="{75A7E45B-C227-4CF5-B1E9-D5BDD9B6637C}"/>
+    <hyperlink ref="A3" r:id="rId122" xr:uid="{D44D3FAD-D28B-4520-B8A5-A29F80BFA189}"/>
+    <hyperlink ref="A131" r:id="rId123" xr:uid="{00F1BCF0-13CA-4B43-8DF3-E453747836E7}"/>
+    <hyperlink ref="A44" r:id="rId124" xr:uid="{E0994650-41C9-4C3F-9BEC-FA80935009D9}"/>
+    <hyperlink ref="A43" r:id="rId125" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{253230BE-7E1B-4968-8C55-FA4364F8CBC5}"/>
+    <hyperlink ref="A73" r:id="rId126" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F1C944A1-19DC-4371-98A1-A2D838E4F269}"/>
+    <hyperlink ref="A74" r:id="rId127" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg/960px-Gilbert_Stuart_-_George_Washington_%28The_Athenaeum_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{FA20EED7-AA47-4E03-BE66-AFC50264306C}"/>
+    <hyperlink ref="A94" r:id="rId128" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BE16BF4-DD65-4F27-BBD5-A6EF014B05B6}"/>
+    <hyperlink ref="A93" r:id="rId129" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg/330px-It%C5%8D_Jakuch%C5%AB_-_White_fowl_and_pine_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE319303-F75E-4837-B1A7-A12164E73405}"/>
+    <hyperlink ref="A92" r:id="rId130" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Fish_and_octopus_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8FE59364-D9F8-4529-B52B-202CBB40D51C}"/>
+    <hyperlink ref="A91" r:id="rId131" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg/960px-%27Old_Pine_Tree_and_Peacock%27_from_the_%27Colorful_Realm_of_Living_Beings%27_by_Ito_Jakuchu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{857FA17F-932C-4DF5-8BF0-6FBF572CA2E9}"/>
+    <hyperlink ref="A36" r:id="rId132" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97334409-644B-4C8F-8DD1-C9739DFDCF00}"/>
+    <hyperlink ref="A132" r:id="rId133" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C3E45888-78FB-469F-88EF-4555AC4C5B33}"/>
+    <hyperlink ref="A160" r:id="rId134" xr:uid="{4DAF9F68-C415-4CF3-9F65-589FC5D5CA2B}"/>
+    <hyperlink ref="A171" r:id="rId135" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0906DB65-B8C5-4B3A-8E90-2873AADBC296}"/>
+    <hyperlink ref="A78" r:id="rId136" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg/960px-The_Immaculate_Conception%2C_by_Giovanni_Battista_Tiepolo%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{31AE0316-09BF-4338-B46B-1C75C21E8095}"/>
+    <hyperlink ref="A62" r:id="rId137" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDEE96F0-6E4A-45D0-9AF3-0D0904CC30FA}"/>
+    <hyperlink ref="A64" r:id="rId138" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg/960px-Venus_Consoling_Love%2C_Fran%C3%A7ois_Boucher%2C_1751.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{43E18F07-A342-4B74-B10C-134C04EF4114}"/>
+    <hyperlink ref="A141" r:id="rId139" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DE7EA9C6-77CF-437A-8102-5BD685E8EE51}"/>
+    <hyperlink ref="A100" r:id="rId140" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F35051B9-00EE-460E-AC95-3A1849B7EDBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau3.xlsx
+++ b/quizzes/peinture-18e-niveau3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0908F4A2-9191-4E1F-8FBC-7C583A778C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C8C45E3-94C2-409E-97B7-B0325143B2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="595">
   <si>
     <t>image</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>210,8 × 151,1 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/19/Labille-Guiard_Robespierre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
     <t>63 × 52 cm</t>
   </si>
   <si>
+    <t>suédoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg/960px-Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -152,6 +161,9 @@
     <t>Portrait de George III</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -188,6 +200,9 @@
     <t>101,6 × 127 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Angelica_Kauffmann_%281741-1807%29_-_Self_Portrait_of_the_Artist_Hesitating_between_the_Arts_of_Music_and_Painting_-_960079_-_National_Trust.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -239,6 +254,9 @@
     <t>1736-1813</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -287,6 +305,9 @@
     <t>152,6 × 214,5 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Benjamin_West_003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -320,6 +341,9 @@
     <t>1721-1780</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Bellotto_View_of_Warsaw_from_Praga.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -476,6 +500,9 @@
     <t>1735-1822</t>
   </si>
   <si>
+    <t>russe</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -587,6 +614,9 @@
     <t>104 × 152 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/da/Goya.pelele.prado.jpg/960px-Goya.pelele.prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -797,6 +827,9 @@
     <t>Encre et couleurs sur soie</t>
   </si>
   <si>
+    <t>chinoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -863,6 +896,9 @@
     <t>76,2 × 63,5 cm</t>
   </si>
   <si>
+    <t>écossaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Henry_Raeburn_%281756-1823%29_-_Sir_John_Sinclair_%281754%E2%80%931835%29%2C_1st_Baronet_of_Ulbster_-_NG_2301_-_National_Galleries_of_Scotland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -927,6 +963,9 @@
   </si>
   <si>
     <t>1716-1800</t>
+  </si>
+  <si>
+    <t>japonaise</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -2347,1051 +2386,1133 @@
       <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="24"/>
+      <c r="I1" s="24" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="25"/>
+        <v>16</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="25"/>
+        <v>30</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="25"/>
+        <v>54</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="4">
         <v>1791</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="25"/>
+        <v>66</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F12" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C13" s="12">
         <v>1775</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14" s="25"/>
+        <v>89</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="25"/>
+        <v>95</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E18" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F19" s="25"/>
       <c r="G19" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="I20" s="25"/>
+        <v>121</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="10" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F21" s="25"/>
       <c r="G21" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="I22" s="25"/>
+        <v>131</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C23" s="12">
         <v>1789</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F23" s="25"/>
       <c r="G23" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="25"/>
+        <v>141</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F25" s="25"/>
       <c r="G25" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F26" s="25"/>
       <c r="G26" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I26" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>139</v>
-      </c>
       <c r="E28" s="20" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F28" s="25"/>
       <c r="G28" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="I28" s="25"/>
+        <v>160</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="I29" s="25"/>
+        <v>166</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="7" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F30" s="25"/>
       <c r="G30" s="25" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I30" s="25"/>
+        <v>171</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="10" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="I32" s="25"/>
+        <v>183</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="6" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="I34" s="25"/>
+        <v>192</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="6" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F35" s="25"/>
       <c r="G35" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="I35" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="10" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F36" s="25"/>
       <c r="G36" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="I36" s="25"/>
+        <v>202</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="10" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C37" s="12">
         <v>1783</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="10" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="F38" s="25"/>
       <c r="G38" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="I38" s="25"/>
+        <v>209</v>
+      </c>
+      <c r="I38" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="10" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C39" s="12">
         <v>1750</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="I40" s="25"/>
+        <v>216</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="6" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F41" s="25"/>
       <c r="G41" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="I41" s="25"/>
+        <v>221</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="K41">
         <f>SUMIF(A:A,"fond rouge")</f>
         <v>0</v>
@@ -3399,2101 +3520,2261 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="6" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I42" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C43" s="4">
         <v>1794</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I43" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="I44" s="25"/>
+        <v>236</v>
+      </c>
+      <c r="I44" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="10" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F45" s="25"/>
       <c r="G45" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="6" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="I46" s="25"/>
+        <v>246</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="I47" s="25"/>
+        <v>253</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="7" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F48" s="25"/>
       <c r="G48" s="25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="I48" s="25"/>
+        <v>81</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="H49" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I49" s="25" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="I50" s="25"/>
+        <v>271</v>
+      </c>
+      <c r="I50" s="25" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="10" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F51" s="25"/>
       <c r="G51" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="I51" s="25"/>
+        <v>276</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="C52" s="7" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F52" s="25"/>
       <c r="G52" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="7" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="I53" s="25"/>
+        <v>286</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="11" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="F54" s="25"/>
       <c r="G54" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="10" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="H55" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C56" s="4">
         <v>1796</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="I56" s="25"/>
+        <v>303</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="10" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="I58" s="25"/>
+        <v>315</v>
+      </c>
+      <c r="I58" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="10" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C59" s="12">
         <v>1794</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H59" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I59" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="6" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="F60" s="25"/>
       <c r="G60" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H60" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="I60" s="25"/>
+        <v>321</v>
+      </c>
+      <c r="I60" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="10" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C61" s="12">
         <v>1791</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F61" s="25"/>
       <c r="G61" s="25" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="H61" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I61" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>299</v>
       </c>
       <c r="C62" s="12">
         <v>1799</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="F62" s="25"/>
       <c r="G62" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H62" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="I62" s="25"/>
+        <v>327</v>
+      </c>
+      <c r="I62" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H63" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="I63" s="25"/>
+        <v>333</v>
+      </c>
+      <c r="I63" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="6" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="F64" s="25"/>
       <c r="G64" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H64" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="I64" s="25"/>
+        <v>337</v>
+      </c>
+      <c r="I64" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="6" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="F65" s="25"/>
       <c r="G65" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H65" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="I65" s="25"/>
+        <v>341</v>
+      </c>
+      <c r="I65" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>316</v>
-      </c>
       <c r="C66" s="11" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="F66" s="25"/>
       <c r="G66" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="I66" s="25"/>
+        <v>344</v>
+      </c>
+      <c r="I66" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="10" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="F67" s="25"/>
       <c r="G67" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="I67" s="25"/>
+        <v>348</v>
+      </c>
+      <c r="I67" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="G68" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H68" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="I68" s="25"/>
+        <v>353</v>
+      </c>
+      <c r="I68" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="6" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F69" s="25"/>
       <c r="G69" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H69" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="I69" s="25"/>
+        <v>357</v>
+      </c>
+      <c r="I69" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="1" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="C70" s="3">
         <v>1721</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="I70" s="25"/>
+        <v>363</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="10" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="C71" s="12">
         <v>1748</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F71" s="25"/>
       <c r="G71" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H71" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I71" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="6" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H72" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I72" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="I73" s="25"/>
+        <v>378</v>
+      </c>
+      <c r="I73" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="6" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="C74" s="9">
         <v>1771</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I74" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I74" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="10" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F75" s="25"/>
       <c r="G75" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>371</v>
-      </c>
-      <c r="I75" s="25"/>
+        <v>384</v>
+      </c>
+      <c r="I75" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="10" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="F76" s="25"/>
       <c r="G76" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H76" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="I76" s="25"/>
+        <v>388</v>
+      </c>
+      <c r="I76" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="6" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="H77" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="I77" s="25"/>
+        <v>395</v>
+      </c>
+      <c r="I77" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="10" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F78" s="25"/>
       <c r="G78" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H78" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I78" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="10" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="F79" s="25"/>
       <c r="G79" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H79" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="I79" s="25"/>
+        <v>403</v>
+      </c>
+      <c r="I79" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="1" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H80" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="I80" s="25"/>
+        <v>407</v>
+      </c>
+      <c r="I80" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="6" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="F81" s="25"/>
       <c r="G81" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H81" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="I81" s="25"/>
+        <v>411</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="10" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="F82" s="25"/>
       <c r="G82" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H82" s="25" t="s">
-        <v>402</v>
-      </c>
-      <c r="I82" s="25"/>
+        <v>415</v>
+      </c>
+      <c r="I82" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="7" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H83" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I83" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="6" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="G84" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="25" t="s">
-        <v>413</v>
-      </c>
-      <c r="I84" s="25"/>
+        <v>426</v>
+      </c>
+      <c r="I84" s="25" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="10" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="F85" s="25"/>
       <c r="G85" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H85" s="25" t="s">
-        <v>416</v>
-      </c>
-      <c r="I85" s="25"/>
+        <v>429</v>
+      </c>
+      <c r="I85" s="25" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H86" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="I86" s="25"/>
+        <v>434</v>
+      </c>
+      <c r="I86" s="25" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="10" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="G87" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H87" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="10" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="G88" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I88" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="G89" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="I89" s="25"/>
+        <v>447</v>
+      </c>
+      <c r="I89" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="10" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="F90" s="25"/>
       <c r="G90" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I90" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="I91" s="25"/>
+        <v>456</v>
+      </c>
+      <c r="I91" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="11" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F92" s="25"/>
       <c r="G92" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="I92" s="25"/>
+        <v>461</v>
+      </c>
+      <c r="I92" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="6" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="G93" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I93" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="10" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I94" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I94" s="25" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="10" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I95" s="25" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="2" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="I96" s="25"/>
+        <v>477</v>
+      </c>
+      <c r="I96" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="11" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="F97" s="25"/>
       <c r="G97" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I97" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="10" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I98" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="6" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="G99" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="I99" s="25"/>
+        <v>492</v>
+      </c>
+      <c r="I99" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="10" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="F100" s="25"/>
       <c r="G100" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H100" s="25" t="s">
-        <v>483</v>
-      </c>
-      <c r="I100" s="25"/>
+        <v>496</v>
+      </c>
+      <c r="I100" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="10" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="F101" s="25"/>
       <c r="G101" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H101" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I101" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="1" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="G102" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H102" s="25" t="s">
-        <v>494</v>
-      </c>
-      <c r="I102" s="25"/>
+        <v>507</v>
+      </c>
+      <c r="I102" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="10" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H103" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="I103" s="25"/>
+        <v>512</v>
+      </c>
+      <c r="I103" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="10" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H104" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I104" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="6" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H105" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="I105" s="25"/>
+        <v>36</v>
+      </c>
+      <c r="I105" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="10" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="F106" s="25"/>
       <c r="G106" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H106" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I106" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="11" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="F107" s="25"/>
       <c r="G107" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H107" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="I107" s="25"/>
+        <v>525</v>
+      </c>
+      <c r="I107" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="2" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="F108" s="25" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="G108" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H108" s="25" t="s">
-        <v>517</v>
-      </c>
-      <c r="I108" s="25"/>
+        <v>530</v>
+      </c>
+      <c r="I108" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="10" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="F109" s="25"/>
       <c r="G109" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H109" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I109" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I109" s="25" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="6" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="F110" s="25" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="G110" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H110" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I110" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I110" s="25" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="1" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="C111" s="4">
         <v>1794</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E111" s="22" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="F111" s="25" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="G111" s="25" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="H111" s="25" t="s">
-        <v>532</v>
-      </c>
-      <c r="I111" s="25"/>
+        <v>545</v>
+      </c>
+      <c r="I111" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="2" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E112" s="21" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="F112" s="25" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="G112" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H112" s="25" t="s">
-        <v>538</v>
-      </c>
-      <c r="I112" s="25"/>
+        <v>551</v>
+      </c>
+      <c r="I112" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="11" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="F113" s="25"/>
       <c r="G113" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H113" s="25" t="s">
-        <v>542</v>
-      </c>
-      <c r="I113" s="25"/>
+        <v>555</v>
+      </c>
+      <c r="I113" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="11" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="F114" s="25"/>
       <c r="G114" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>545</v>
-      </c>
-      <c r="I114" s="25"/>
+        <v>558</v>
+      </c>
+      <c r="I114" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="10" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="G115" s="25" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I115" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I115" s="25" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="10" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I116" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I116" s="25" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="1" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E117" s="22" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>561</v>
-      </c>
-      <c r="I117" s="25"/>
+        <v>574</v>
+      </c>
+      <c r="I117" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="10" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I118" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I118" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="10" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="C119" s="15">
         <v>1735</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="F119" s="25" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="G119" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H119" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I119" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I119" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="10" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="C120" s="15">
         <v>1735</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="F120" s="25" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="G120" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H120" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I120" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="I120" s="25" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="10" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="C121" s="15">
         <v>1791</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E121" s="23" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="F121" s="25" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="G121" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H121" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="I121" s="25"/>
+        <v>594</v>
+      </c>
+      <c r="I121" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
